--- a/docs/uart_report.xlsx
+++ b/docs/uart_report.xlsx
@@ -82,10 +82,10 @@
     <t xml:space="preserve"># SharedData Build 6298862 on Thu Nov 13 04:50:51 MST 2025</t>
   </si>
   <si>
-    <t xml:space="preserve"># Start of session at: Wed Mar 25 22:44:26 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Process ID         : 123160</t>
+    <t xml:space="preserve"># Start of session at: Thu Apr  9 14:11:49 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Process ID         : 159690</t>
   </si>
   <si>
     <t xml:space="preserve"># Current directory  : /home/tim/projects/uart/synthesis</t>
@@ -130,7 +130,7 @@
     <t xml:space="preserve"># Total Virtual      : 42067 MB</t>
   </si>
   <si>
-    <t xml:space="preserve"># Available Virtual  : 33748 MB</t>
+    <t xml:space="preserve"># Available Virtual  : 37727 MB</t>
   </si>
   <si>
     <t xml:space="preserve">source run_synthesis.tcl</t>
@@ -574,13 +574,13 @@
     <t xml:space="preserve">INFO: [Synth 8-7078] Launching helper process for spawning children vivado processes</t>
   </si>
   <si>
-    <t xml:space="preserve">INFO: [Synth 8-7075] Helper process launched with PID 123227</t>
+    <t xml:space="preserve">INFO: [Synth 8-7075] Helper process launched with PID 159749</t>
   </si>
   <si>
     <t>---------------------------------------------------------------------------------</t>
   </si>
   <si>
-    <t xml:space="preserve">Starting RTL Elaboration : Time (s): cpu = 00:00:04 ; elapsed = 00:00:04 . Memory (MB): peak = 2572.848 ; gain = 480.785 ; free physical = 15519 ; free virtual = 30775</t>
+    <t xml:space="preserve">Starting RTL Elaboration : Time (s): cpu = 00:00:04 ; elapsed = 00:00:04 . Memory (MB): peak = 2573.195 ; gain = 480.098 ; free physical = 15398 ; free virtual = 34524</t>
   </si>
   <si>
     <t xml:space="preserve">WARNING: [Synth 8-4747] shared variables must be of a protected type [/home/tim/projects/uart/cores/open-logic/src/base/vhdl/olo_base_ram_tdp.vhd:263]</t>
@@ -630,7 +630,7 @@
     <t xml:space="preserve">INFO: [Synth 8-638] synthesizing module 'TOP_FPGA' [/home/tim/projects/uart/sources/top_fpga/top_fpga.vhd:93]</t>
   </si>
   <si>
-    <t xml:space="preserve">    Parameter G_GIT_ID bound to: 32'b00011110011000110000010110100111</t>
+    <t xml:space="preserve">    Parameter G_GIT_ID bound to: 32'b01110101110011111011010010010011</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Synth 8-3491] module 'clk_wiz_0' declared at '/home/tim/projects/uart/synthesis/uart/uart.gen/sources_1/ip/clk_wiz_0/clk_wiz_0.v:66' bound to instance 'inst_pll' of component 'clk_wiz_0' [/home/tim/projects/uart/sources/top_fpga/top_fpga.vhd:187]</t>
@@ -735,7 +735,7 @@
     <t xml:space="preserve">INFO: [Synth 8-256] done synthesizing module 'olo_intf_sync' (0#1) [/home/tim/projects/uart/cores/open-logic/src/intf/vhdl/olo_intf_sync.vhd:53]</t>
   </si>
   <si>
-    <t xml:space="preserve">INFO: [Synth 8-638] synthesizing module 'UART' [/home/tim/projects/uart/sources/uart/uart.vhd:80]</t>
+    <t xml:space="preserve">INFO: [Synth 8-638] synthesizing module 'UART' [/home/tim/projects/uart/sources/uart/uart.vhd:81]</t>
   </si>
   <si>
     <t xml:space="preserve">    Parameter G_CLK_FREQ_HZ bound to: 50000000 - type: integer</t>
@@ -759,16 +759,16 @@
     <t xml:space="preserve">INFO: [Synth 8-256] done synthesizing module 'UART_RX' (0#1) [/home/tim/projects/uart/sources/uart/uart_rx.vhd:73]</t>
   </si>
   <si>
-    <t xml:space="preserve">INFO: [Synth 8-256] done synthesizing module 'UART' (0#1) [/home/tim/projects/uart/sources/uart/uart.vhd:80]</t>
+    <t xml:space="preserve">INFO: [Synth 8-256] done synthesizing module 'UART' (0#1) [/home/tim/projects/uart/sources/uart/uart.vhd:81]</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Synth 8-638] synthesizing module 'REGFILE' [/home/tim/projects/uart/sources/regfile/regfile.vhd:88]</t>
   </si>
   <si>
-    <t xml:space="preserve">    Parameter G_GIT_ID_MSB bound to: 16'b0001111001100011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Parameter G_GIT_ID_LSB bound to: 16'b0000010110100111</t>
+    <t xml:space="preserve">    Parameter G_GIT_ID_MSB bound to: 16'b0111010111001111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Parameter G_GIT_ID_LSB bound to: 16'b1011010010010011</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Synth 8-256] done synthesizing module 'REGFILE' (0#1) [/home/tim/projects/uart/sources/regfile/regfile.vhd:88]</t>
@@ -891,19 +891,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Finished RTL Elaboration : Time (s): cpu = 00:00:05 ; elapsed = 00:00:06 . Memory (MB): peak = 2669.816 ; gain = 577.754 ; free physical = 15424 ; free virtual = 30682</t>
+    <t xml:space="preserve">Finished RTL Elaboration : Time (s): cpu = 00:00:05 ; elapsed = 00:00:06 . Memory (MB): peak = 2670.164 ; gain = 577.066 ; free physical = 15301 ; free virtual = 34428</t>
   </si>
   <si>
     <t xml:space="preserve">Start Handling Custom Attributes</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Handling Custom Attributes : Time (s): cpu = 00:00:06 ; elapsed = 00:00:06 . Memory (MB): peak = 2681.691 ; gain = 589.629 ; free physical = 15424 ; free virtual = 30682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finished RTL Optimization Phase 1 : Time (s): cpu = 00:00:06 ; elapsed = 00:00:06 . Memory (MB): peak = 2681.691 ; gain = 589.629 ; free physical = 15424 ; free virtual = 30682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 2684.660 ; gain = 0.000 ; free physical = 15424 ; free virtual = 30682</t>
+    <t xml:space="preserve">Finished Handling Custom Attributes : Time (s): cpu = 00:00:05 ; elapsed = 00:00:06 . Memory (MB): peak = 2682.039 ; gain = 588.941 ; free physical = 15301 ; free virtual = 34428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finished RTL Optimization Phase 1 : Time (s): cpu = 00:00:05 ; elapsed = 00:00:06 . Memory (MB): peak = 2682.039 ; gain = 588.941 ; free physical = 15301 ; free virtual = 34428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00.01 . Memory (MB): peak = 2682.039 ; gain = 0.000 ; free physical = 15297 ; free virtual = 34424</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Netlist 29-17] Analyzing 1 Unisim elements for replacement</t>
@@ -960,7 +960,7 @@
     <t xml:space="preserve">Completed Processing XDC Constraints</t>
   </si>
   <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 2798.461 ; gain = 0.000 ; free physical = 15419 ; free virtual = 30677</t>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 2789.840 ; gain = 0.000 ; free physical = 15295 ; free virtual = 34421</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Project 1-111] Unisim Transformation Summary:</t>
@@ -969,10 +969,10 @@
     <t xml:space="preserve">No Unisim elements were transformed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Constraint Validation Runtime : Time (s): cpu = 00:00:00.01 ; elapsed = 00:00:00 . Memory (MB): peak = 2798.496 ; gain = 0.000 ; free physical = 15420 ; free virtual = 30677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finished Constraint Validation : Time (s): cpu = 00:00:11 ; elapsed = 00:00:11 . Memory (MB): peak = 2798.496 ; gain = 706.434 ; free physical = 15433 ; free virtual = 30690</t>
+    <t xml:space="preserve">Constraint Validation Runtime : Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 2789.875 ; gain = 0.000 ; free physical = 15295 ; free virtual = 34421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finished Constraint Validation : Time (s): cpu = 00:00:11 ; elapsed = 00:00:11 . Memory (MB): peak = 2789.875 ; gain = 696.777 ; free physical = 15332 ; free virtual = 34459</t>
   </si>
   <si>
     <t xml:space="preserve">Start Loading Part and Timing Information</t>
@@ -981,13 +981,13 @@
     <t xml:space="preserve">Loading part: xc7z020clg484-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Loading Part and Timing Information : Time (s): cpu = 00:00:11 ; elapsed = 00:00:11 . Memory (MB): peak = 2806.465 ; gain = 714.402 ; free physical = 15433 ; free virtual = 30690</t>
+    <t xml:space="preserve">Finished Loading Part and Timing Information : Time (s): cpu = 00:00:11 ; elapsed = 00:00:11 . Memory (MB): peak = 2797.844 ; gain = 704.746 ; free physical = 15332 ; free virtual = 34459</t>
   </si>
   <si>
     <t xml:space="preserve">Start Applying 'set_property' XDC Constraints</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished applying 'set_property' XDC Constraints : Time (s): cpu = 00:00:11 ; elapsed = 00:00:11 . Memory (MB): peak = 2806.465 ; gain = 714.402 ; free physical = 15433 ; free virtual = 30690</t>
+    <t xml:space="preserve">Finished applying 'set_property' XDC Constraints : Time (s): cpu = 00:00:11 ; elapsed = 00:00:11 . Memory (MB): peak = 2797.844 ; gain = 704.746 ; free physical = 15332 ; free virtual = 34459</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Synth 8-802] inferred FSM for state register 'current_state_reg' in module 'UART_TX'</t>
@@ -1092,7 +1092,7 @@
     <t xml:space="preserve">INFO: [Synth 8-3354] encoded FSM with state register 'current_state_reg' using encoding 'one-hot' in module 'SPI_MASTER'</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished RTL Optimization Phase 2 : Time (s): cpu = 00:00:12 ; elapsed = 00:00:12 . Memory (MB): peak = 2806.465 ; gain = 714.402 ; free physical = 15438 ; free virtual = 30697</t>
+    <t xml:space="preserve">Finished RTL Optimization Phase 2 : Time (s): cpu = 00:00:11 ; elapsed = 00:00:12 . Memory (MB): peak = 2797.844 ; gain = 704.746 ; free physical = 15342 ; free virtual = 34470</t>
   </si>
   <si>
     <t xml:space="preserve">Start RTL Component Statistics</t>
@@ -1257,25 +1257,25 @@
     <t xml:space="preserve">Start Cross Boundary and Area Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Cross Boundary and Area Optimization : Time (s): cpu = 00:00:15 ; elapsed = 00:00:15 . Memory (MB): peak = 2806.465 ; gain = 714.402 ; free physical = 15429 ; free virtual = 30692</t>
+    <t xml:space="preserve">Finished Cross Boundary and Area Optimization : Time (s): cpu = 00:00:15 ; elapsed = 00:00:15 . Memory (MB): peak = 2797.844 ; gain = 704.746 ; free physical = 15362 ; free virtual = 34494</t>
   </si>
   <si>
     <t xml:space="preserve">Start Applying XDC Timing Constraints</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Applying XDC Timing Constraints : Time (s): cpu = 00:00:19 ; elapsed = 00:00:19 . Memory (MB): peak = 2841.465 ; gain = 749.402 ; free physical = 15375 ; free virtual = 30639</t>
+    <t xml:space="preserve">Finished Applying XDC Timing Constraints : Time (s): cpu = 00:00:18 ; elapsed = 00:00:19 . Memory (MB): peak = 2840.844 ; gain = 747.746 ; free physical = 15326 ; free virtual = 34458</t>
   </si>
   <si>
     <t xml:space="preserve">Start Timing Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Timing Optimization : Time (s): cpu = 00:00:19 ; elapsed = 00:00:19 . Memory (MB): peak = 2842.465 ; gain = 750.402 ; free physical = 15375 ; free virtual = 30639</t>
+    <t xml:space="preserve">Finished Timing Optimization : Time (s): cpu = 00:00:19 ; elapsed = 00:00:19 . Memory (MB): peak = 2841.844 ; gain = 748.746 ; free physical = 15326 ; free virtual = 34458</t>
   </si>
   <si>
     <t xml:space="preserve">Start Technology Mapping</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Technology Mapping : Time (s): cpu = 00:00:19 ; elapsed = 00:00:19 . Memory (MB): peak = 2861.496 ; gain = 769.434 ; free physical = 15352 ; free virtual = 30615</t>
+    <t xml:space="preserve">Finished Technology Mapping : Time (s): cpu = 00:00:19 ; elapsed = 00:00:19 . Memory (MB): peak = 2860.875 ; gain = 767.777 ; free physical = 15310 ; free virtual = 34442</t>
   </si>
   <si>
     <t xml:space="preserve">Start IO Insertion</t>
@@ -1293,34 +1293,34 @@
     <t xml:space="preserve">Finished Final Netlist Cleanup</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished IO Insertion : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.309 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
+    <t xml:space="preserve">Finished IO Insertion : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.688 ; gain = 946.590 ; free physical = 15147 ; free virtual = 34280</t>
   </si>
   <si>
     <t xml:space="preserve">Start Renaming Generated Instances</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Renaming Generated Instances : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.309 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
+    <t xml:space="preserve">Finished Renaming Generated Instances : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.688 ; gain = 946.590 ; free physical = 15147 ; free virtual = 34280</t>
   </si>
   <si>
     <t xml:space="preserve">Start Rebuilding User Hierarchy</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Rebuilding User Hierarchy : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.309 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
+    <t xml:space="preserve">Finished Rebuilding User Hierarchy : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.688 ; gain = 946.590 ; free physical = 15147 ; free virtual = 34280</t>
   </si>
   <si>
     <t xml:space="preserve">Start Renaming Generated Ports</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Renaming Generated Ports : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.309 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finished Handling Custom Attributes : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.309 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
+    <t xml:space="preserve">Finished Renaming Generated Ports : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.688 ; gain = 946.590 ; free physical = 15147 ; free virtual = 34280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finished Handling Custom Attributes : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.688 ; gain = 946.590 ; free physical = 15147 ; free virtual = 34280</t>
   </si>
   <si>
     <t xml:space="preserve">Start Renaming Generated Nets</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Renaming Generated Nets : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.309 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
+    <t xml:space="preserve">Finished Renaming Generated Nets : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.688 ; gain = 946.590 ; free physical = 15147 ; free virtual = 34280</t>
   </si>
   <si>
     <t xml:space="preserve">Start Writing Synthesis Report</t>
@@ -1350,31 +1350,31 @@
     <t xml:space="preserve">|2     |LUT1      |     2|</t>
   </si>
   <si>
-    <t xml:space="preserve">|3     |LUT2      |    34|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|4     |LUT3      |    29|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|5     |LUT4      |    42|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|6     |LUT5      |    59|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|7     |LUT6      |   132|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|8     |MUXF7     |     4|</t>
+    <t xml:space="preserve">|3     |LUT2      |    33|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|4     |LUT3      |    31|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|5     |LUT4      |    50|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|6     |LUT5      |    58|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|7     |LUT6      |   121|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|8     |MUXF7     |     9|</t>
   </si>
   <si>
     <t xml:space="preserve">|9     |PLLE2_ADV |     1|</t>
   </si>
   <si>
-    <t xml:space="preserve">|10    |FDCE      |   231|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|11    |FDPE      |    52|</t>
+    <t xml:space="preserve">|10    |FDCE      |   228|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|11    |FDPE      |    55|</t>
   </si>
   <si>
     <t xml:space="preserve">|12    |FDRE      |    68|</t>
@@ -1386,25 +1386,25 @@
     <t xml:space="preserve">|14    |OBUF      |    19|</t>
   </si>
   <si>
-    <t xml:space="preserve">Finished Writing Synthesis Report : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.309 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
+    <t xml:space="preserve">Finished Writing Synthesis Report : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.688 ; gain = 946.590 ; free physical = 15147 ; free virtual = 34280</t>
   </si>
   <si>
     <t xml:space="preserve">Synthesis finished with 0 errors, 0 critical warnings and 0 warnings.</t>
   </si>
   <si>
-    <t xml:space="preserve">Synthesis Optimization Runtime : Time (s): cpu = 00:00:22 ; elapsed = 00:00:22 . Memory (MB): peak = 3039.309 ; gain = 830.441 ; free physical = 15208 ; free virtual = 30472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synthesis Optimization Complete : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.316 ; gain = 947.246 ; free physical = 15208 ; free virtual = 30472</t>
+    <t xml:space="preserve">Synthesis Optimization Runtime : Time (s): cpu = 00:00:22 ; elapsed = 00:00:22 . Memory (MB): peak = 3039.688 ; gain = 838.754 ; free physical = 15150 ; free virtual = 34282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synthesis Optimization Complete : Time (s): cpu = 00:00:22 ; elapsed = 00:00:23 . Memory (MB): peak = 3039.695 ; gain = 946.590 ; free physical = 15150 ; free virtual = 34283</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Project 1-571] Translating synthesized netlist</t>
   </si>
   <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3039.316 ; gain = 0.000 ; free physical = 15208 ; free virtual = 30472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO: [Netlist 29-17] Analyzing 5 Unisim elements for replacement</t>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00.01 ; elapsed = 00:00:00 . Memory (MB): peak = 3039.695 ; gain = 0.000 ; free physical = 15150 ; free virtual = 34283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Netlist 29-17] Analyzing 10 Unisim elements for replacement</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Timing 38-35] Done setting XDC timing constraints. [/home/tim/projects/uart/synthesis/uart/uart.gen/sources_1/ip/clk_wiz_0/clk_wiz_0.xdc:54]</t>
@@ -1515,10 +1515,10 @@
     <t xml:space="preserve">INFO: [Opt 31-138] Pushed 0 inverter(s) to 0 load pin(s).</t>
   </si>
   <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3564.164 ; gain = 0.000 ; free physical = 14976 ; free virtual = 30240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synth Design complete | Checksum: c77a6c22</t>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3564.543 ; gain = 0.000 ; free physical = 14938 ; free virtual = 34071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synth Design complete | Checksum: 8a2ecec1</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Common 17-83] Releasing license: Synthesis</t>
@@ -1530,13 +1530,13 @@
     <t xml:space="preserve">synth_design completed successfully</t>
   </si>
   <si>
-    <t xml:space="preserve">synth_design: Time (s): cpu = 00:00:33 ; elapsed = 00:00:30 . Memory (MB): peak = 3564.199 ; gain = 1472.227 ; free physical = 14974 ; free virtual = 30238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO: [Common 17-2834] synth_design peak Physical Memory [PSS] (MB): overall = 2604.442; main = 2604.442; forked = 345.133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO: [Common 17-2834] synth_design peak Virtual Memory [VSS] (MB): overall = 4524.285; main = 3564.168; forked = 1645.785</t>
+    <t xml:space="preserve">synth_design: Time (s): cpu = 00:00:33 ; elapsed = 00:00:31 . Memory (MB): peak = 3564.578 ; gain = 1471.570 ; free physical = 14938 ; free virtual = 34071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Common 17-2834] synth_design peak Physical Memory [PSS] (MB): overall = 2609.023; main = 2609.023; forked = 345.112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Common 17-2834] synth_design peak Virtual Memory [VSS] (MB): overall = 4527.664; main = 3564.547; forked = 1645.785</t>
   </si>
   <si>
     <t xml:space="preserve"># file mkdir "${RESULTS_DIR}/synth"</t>
@@ -1618,16 +1618,16 @@
     <t xml:space="preserve">INFO: [Project 1-462] Please refer to the DRC report (report_drc) for more information.</t>
   </si>
   <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.91 ; elapsed = 00:00:00.42 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14981 ; free virtual = 30245</t>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.84 ; elapsed = 00:00:00.42 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14937 ; free virtual = 34070</t>
   </si>
   <si>
     <t xml:space="preserve">Starting Cache Timing Information Task</t>
   </si>
   <si>
-    <t xml:space="preserve">Ending Cache Timing Information Task | Checksum: 1840cb1ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14981 ; free virtual = 30245</t>
+    <t xml:space="preserve">Ending Cache Timing Information Task | Checksum: 196b13c37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14937 ; free virtual = 34070</t>
   </si>
   <si>
     <t xml:space="preserve">Starting Logic Optimization Task</t>
@@ -1639,19 +1639,19 @@
     <t xml:space="preserve">Phase 1.1 Core Generation And Design Setup</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1.1 Core Generation And Design Setup | Checksum: 1840cb1ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30240</t>
+    <t xml:space="preserve">Phase 1.1 Core Generation And Design Setup | Checksum: 196b13c37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00.01 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 1.2 Setup Constraints And Sort Netlist</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1.2 Setup Constraints And Sort Netlist | Checksum: 1840cb1ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 Initialization | Checksum: 1840cb1ea</t>
+    <t xml:space="preserve">Phase 1.2 Setup Constraints And Sort Netlist | Checksum: 196b13c37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 1 Initialization | Checksum: 196b13c37</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2 Timer Update And Timing Data Collection</t>
@@ -1660,31 +1660,28 @@
     <t xml:space="preserve">Phase 2.1 Detect if minReqCache needed</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.1 Detect if minReqCache needed | Checksum: 1840cb1ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.01 ; elapsed = 00:00:00.01 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30240</t>
+    <t xml:space="preserve">Phase 2.1 Detect if minReqCache needed | Checksum: 196b13c37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.01 ; elapsed = 00:00:00.01 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.2 Timer Update</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.2 Timer Update | Checksum: 1840cb1ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.06 ; elapsed = 00:00:00.02 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
+    <t xml:space="preserve">Phase 2.2 Timer Update | Checksum: 196b13c37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.06 ; elapsed = 00:00:00.03 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.3 Timing Data Collection</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.3 Timing Data Collection | Checksum: 1840cb1ea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.07 ; elapsed = 00:00:00.03 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 2 Timer Update And Timing Data Collection | Checksum: 1840cb1ea</t>
+    <t xml:space="preserve">Phase 2.3 Timing Data Collection | Checksum: 196b13c37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 2 Timer Update And Timing Data Collection | Checksum: 196b13c37</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3 Retarget</t>
@@ -1702,13 +1699,13 @@
     <t xml:space="preserve">INFO: [Opt 31-49] Retargeted 0 cell(s).</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3 Retarget | Checksum: 135ca414c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.15 ; elapsed = 00:00:00.05 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retarget | Checksum: 135ca414c</t>
+    <t xml:space="preserve">Phase 3 Retarget | Checksum: 11eeb3c59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.15 ; elapsed = 00:00:00.05 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retarget | Checksum: 11eeb3c59</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Opt 31-389] Phase Retarget created 0 cells and removed 2 cells</t>
@@ -1720,13 +1717,13 @@
     <t xml:space="preserve">Phase 4 Constant propagation</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 4 Constant propagation | Checksum: 135ca414c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.17 ; elapsed = 00:00:00.05 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constant propagation | Checksum: 135ca414c</t>
+    <t xml:space="preserve">Phase 4 Constant propagation | Checksum: 11eeb3c59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.17 ; elapsed = 00:00:00.06 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constant propagation | Checksum: 11eeb3c59</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Opt 31-389] Phase Constant propagation created 0 cells and removed 0 cells</t>
@@ -1738,16 +1735,13 @@
     <t xml:space="preserve">INFO: [Constraints 18-11670] Building netlist checker database with flags, 0x8</t>
   </si>
   <si>
-    <t xml:space="preserve">Done building netlist checker database: Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 5 Sweep | Checksum: a1bc9223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.18 ; elapsed = 00:00:00.06 . Memory (MB): peak = 3564.199 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweep | Checksum: a1bc9223</t>
+    <t xml:space="preserve">Done building netlist checker database: Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3564.578 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 5 Sweep | Checksum: aaf48d30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweep | Checksum: aaf48d30</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Opt 31-389] Phase Sweep created 0 cells and removed 0 cells</t>
@@ -1759,13 +1753,13 @@
     <t xml:space="preserve">Phase 6 BUFG optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 6 BUFG optimization | Checksum: a1bc9223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.19 ; elapsed = 00:00:00.07 . Memory (MB): peak = 3596.180 ; gain = 31.980 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUFG optimization | Checksum: a1bc9223</t>
+    <t xml:space="preserve">Phase 6 BUFG optimization | Checksum: aaf48d30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.18 ; elapsed = 00:00:00.07 . Memory (MB): peak = 3596.559 ; gain = 31.980 ; free physical = 14932 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUFG optimization | Checksum: aaf48d30</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Opt 31-662] Phase BUFG optimization created 0 cells of which 0 are BUFGs and removed 0 cells.</t>
@@ -1777,13 +1771,10 @@
     <t xml:space="preserve">INFO: [Opt 31-1064] SRL Remap converted 0 SRLs to 0 registers and converted 0 registers of register chains to 0 SRLs</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 7 Shift Register Optimization | Checksum: a1bc9223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.2 ; elapsed = 00:00:00.07 . Memory (MB): peak = 3596.180 ; gain = 31.980 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shift Register Optimization | Checksum: a1bc9223</t>
+    <t xml:space="preserve">Phase 7 Shift Register Optimization | Checksum: aaf48d30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shift Register Optimization | Checksum: aaf48d30</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Opt 31-389] Phase Shift Register Optimization created 0 cells and removed 0 cells</t>
@@ -1792,13 +1783,13 @@
     <t xml:space="preserve">Phase 8 Post Processing Netlist</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 8 Post Processing Netlist | Checksum: a1bc9223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.2 ; elapsed = 00:00:00.08 . Memory (MB): peak = 3596.180 ; gain = 31.980 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Processing Netlist | Checksum: a1bc9223</t>
+    <t xml:space="preserve">Phase 8 Post Processing Netlist | Checksum: aaf48d30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.19 ; elapsed = 00:00:00.08 . Memory (MB): peak = 3596.559 ; gain = 31.980 ; free physical = 14932 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post Processing Netlist | Checksum: aaf48d30</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Opt 31-389] Phase Post Processing Netlist created 0 cells and removed 0 cells</t>
@@ -1810,10 +1801,7 @@
     <t xml:space="preserve">Phase 9.1 Finalizing Design Cores and Updating Shapes</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 9.1 Finalizing Design Cores and Updating Shapes | Checksum: 994f7830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.21 ; elapsed = 00:00:00.08 . Memory (MB): peak = 3596.180 ; gain = 31.980 ; free physical = 14977 ; free virtual = 30241</t>
+    <t xml:space="preserve">Phase 9.1 Finalizing Design Cores and Updating Shapes | Checksum: b36ff33d</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 9.2 Verifying Netlist Connectivity</t>
@@ -1822,13 +1810,13 @@
     <t xml:space="preserve">Starting Connectivity Check Task</t>
   </si>
   <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.180 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 9.2 Verifying Netlist Connectivity | Checksum: 994f7830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 9 Finalization | Checksum: 994f7830</t>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.559 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 9.2 Verifying Netlist Connectivity | Checksum: b36ff33d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 9 Finalization | Checksum: b36ff33d</t>
   </si>
   <si>
     <t xml:space="preserve">Opt_design Change Summary</t>
@@ -1861,10 +1849,10 @@
     <t xml:space="preserve">|  Post Processing Netlist      |               0  |               0  |                                              0  |</t>
   </si>
   <si>
-    <t xml:space="preserve">Ending Logic Optimization Task | Checksum: 994f7830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.21 ; elapsed = 00:00:00.09 . Memory (MB): peak = 3596.180 ; gain = 31.980 ; free physical = 14977 ; free virtual = 30241</t>
+    <t xml:space="preserve">Ending Logic Optimization Task | Checksum: b36ff33d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.19 ; elapsed = 00:00:00.09 . Memory (MB): peak = 3596.559 ; gain = 31.980 ; free physical = 14932 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">Starting Power Optimization Task</t>
@@ -1873,16 +1861,19 @@
     <t xml:space="preserve">INFO: [Pwropt 34-132] Skipping clock gating for clocks with a period &lt; 2.00 ns.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ending Power Optimization Task | Checksum: 994f7830</t>
+    <t xml:space="preserve">Ending Power Optimization Task | Checksum: b36ff33d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00.01 . Memory (MB): peak = 3596.559 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">Starting Final Cleanup Task</t>
   </si>
   <si>
-    <t xml:space="preserve">Ending Final Cleanup Task | Checksum: 994f7830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.180 ; gain = 0.000 ; free physical = 14977 ; free virtual = 30241</t>
+    <t xml:space="preserve">Ending Final Cleanup Task | Checksum: b36ff33d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.559 ; gain = 0.000 ; free physical = 14932 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Common 17-83] Releasing license: Implementation</t>
@@ -1924,46 +1915,49 @@
     <t xml:space="preserve">Phase 1.1 Placer Initialization Netlist Sorting</t>
   </si>
   <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.180 ; gain = 0.000 ; free physical = 14980 ; free virtual = 30244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1.1 Placer Initialization Netlist Sorting | Checksum: 7f16ce99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.180 ; gain = 0.000 ; free physical = 14980 ; free virtual = 30244</t>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.559 ; gain = 0.000 ; free physical = 14933 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 1.1 Placer Initialization Netlist Sorting | Checksum: 91e38a26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.559 ; gain = 0.000 ; free physical = 14933 ; free virtual = 34065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00.01 ; elapsed = 00:00:00 . Memory (MB): peak = 3596.559 ; gain = 0.000 ; free physical = 14933 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 1.2 IO Placement/ Clock Placement/ Build Placer Device</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1.2 IO Placement/ Clock Placement/ Build Placer Device | Checksum: fd1a80be</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.41 ; elapsed = 00:00:00.12 . Memory (MB): peak = 3596.180 ; gain = 0.000 ; free physical = 14981 ; free virtual = 30244</t>
+    <t xml:space="preserve">Phase 1.2 IO Placement/ Clock Placement/ Build Placer Device | Checksum: 147aa2665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.41 ; elapsed = 00:00:00.11 . Memory (MB): peak = 3596.559 ; gain = 0.000 ; free physical = 14933 ; free virtual = 34065</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 1.3 Build Placer Netlist Model</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1.3 Build Placer Netlist Model | Checksum: 162f14eb1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.91 ; elapsed = 00:00:00.26 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14981 ; free virtual = 30244</t>
+    <t xml:space="preserve">Phase 1.3 Build Placer Netlist Model | Checksum: 1bf130e57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.88 ; elapsed = 00:00:00.25 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14930 ; free virtual = 34063</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 1.4 Constrain Clocks/Macros</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1.4 Constrain Clocks/Macros | Checksum: 162f14eb1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.92 ; elapsed = 00:00:00.26 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14981 ; free virtual = 30244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 Placer Initialization | Checksum: 162f14eb1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.93 ; elapsed = 00:00:00.27 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14981 ; free virtual = 30244</t>
+    <t xml:space="preserve">Phase 1.4 Constrain Clocks/Macros | Checksum: 1bf130e57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.89 ; elapsed = 00:00:00.26 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14930 ; free virtual = 34063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 1 Placer Initialization | Checksum: 1bf130e57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.9 ; elapsed = 00:00:00.26 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14930 ; free virtual = 34063</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2 Global Placement</t>
@@ -1972,34 +1966,37 @@
     <t xml:space="preserve">Phase 2.1 Floorplanning</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.1 Floorplanning | Checksum: 1016b0f26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:01 ; elapsed = 00:00:00.34 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14971 ; free virtual = 30235</t>
+    <t xml:space="preserve">Phase 2.1 Floorplanning | Checksum: 20e442574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:01 ; elapsed = 00:00:00.34 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14914 ; free virtual = 34047</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.2 Update Timing before SLR Path Opt</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.2 Update Timing before SLR Path Opt | Checksum: 1dea8b1fe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:01 ; elapsed = 00:00:00.4 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 15005 ; free virtual = 30268</t>
+    <t xml:space="preserve">Phase 2.2 Update Timing before SLR Path Opt | Checksum: 20c2b16d0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:01 ; elapsed = 00:00:00.39 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14945 ; free virtual = 34078</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.3 Post-Processing in Floorplanning</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.3 Post-Processing in Floorplanning | Checksum: 1dea8b1fe</t>
+    <t xml:space="preserve">Phase 2.3 Post-Processing in Floorplanning | Checksum: 20c2b16d0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:01 ; elapsed = 00:00:00.4 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14945 ; free virtual = 34078</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.4 Global Place Phase1</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.4 Global Place Phase1 | Checksum: 1258c2c0e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:04 ; elapsed = 00:00:01 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14972 ; free virtual = 30236</t>
+    <t xml:space="preserve">Phase 2.4 Global Place Phase1 | Checksum: 1f429912b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:04 ; elapsed = 00:00:00.99 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14943 ; free virtual = 34076</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.5 Global Place Phase2</t>
@@ -2008,7 +2005,10 @@
     <t xml:space="preserve">Phase 2.5.1 UpdateTiming Before Physical Synthesis</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.5.1 UpdateTiming Before Physical Synthesis | Checksum: 1258c2c0e</t>
+    <t xml:space="preserve">Phase 2.5.1 UpdateTiming Before Physical Synthesis | Checksum: 1f429912b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:04 ; elapsed = 00:00:01 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14945 ; free virtual = 34078</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.5.2 Physical Synthesis In Placer</t>
@@ -2050,7 +2050,7 @@
     <t xml:space="preserve">INFO: [Physopt 32-949] No candidate nets found for dynamic/static region interface net replication</t>
   </si>
   <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14972 ; free virtual = 30236</t>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14945 ; free virtual = 34078</t>
   </si>
   <si>
     <t xml:space="preserve">Summary of Physical Synthesis Optimizations</t>
@@ -2095,19 +2095,19 @@
     <t xml:space="preserve">|  Total                                            |            0  |              1  |                     1  |           0  |           4  |  00:00:00  |</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.5.2 Physical Synthesis In Placer | Checksum: 23902987e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:04 ; elapsed = 00:00:01 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14972 ; free virtual = 30235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 2.5 Global Place Phase2 | Checksum: 20fd41571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:05 ; elapsed = 00:00:01 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14971 ; free virtual = 30235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 2 Global Placement | Checksum: 20fd41571</t>
+    <t xml:space="preserve">Phase 2.5.2 Physical Synthesis In Placer | Checksum: 223843783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:04 ; elapsed = 00:00:01 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14944 ; free virtual = 34077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 2.5 Global Place Phase2 | Checksum: 14683b826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:05 ; elapsed = 00:00:01 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14944 ; free virtual = 34076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 2 Global Placement | Checksum: 14683b826</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3 Detail Placement</t>
@@ -2116,55 +2116,55 @@
     <t xml:space="preserve">Phase 3.1 Commit Multi Column Macros</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3.1 Commit Multi Column Macros | Checksum: 1dc3cf20f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:05 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14971 ; free virtual = 30234</t>
+    <t xml:space="preserve">Phase 3.1 Commit Multi Column Macros | Checksum: 158a4c4ac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:05 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14943 ; free virtual = 34076</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3.2 Commit Most Macros &amp; LUTRAMs</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3.2 Commit Most Macros &amp; LUTRAMs | Checksum: 1c7f759e4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:05 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14970 ; free virtual = 30234</t>
+    <t xml:space="preserve">Phase 3.2 Commit Most Macros &amp; LUTRAMs | Checksum: 10d662a87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:05 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14942 ; free virtual = 34075</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3.3 Area Swap Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3.3 Area Swap Optimization | Checksum: 21b89455b</t>
+    <t xml:space="preserve">Phase 3.3 Area Swap Optimization | Checksum: 19f686901</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3.4 Pipeline Register Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3.4 Pipeline Register Optimization | Checksum: 262b68912</t>
+    <t xml:space="preserve">Phase 3.4 Pipeline Register Optimization | Checksum: 18f89894e</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3.5 Small Shape Detail Placement</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3.5 Small Shape Detail Placement | Checksum: 1e2adee11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:06 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14969 ; free virtual = 30233</t>
+    <t xml:space="preserve">Phase 3.5 Small Shape Detail Placement | Checksum: 2728bdf19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:06 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.602 ; gain = 39.043 ; free physical = 14941 ; free virtual = 34074</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3.6 Re-assign LUT pins</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3.6 Re-assign LUT pins | Checksum: 1a38bb0c2</t>
+    <t xml:space="preserve">Phase 3.6 Re-assign LUT pins | Checksum: 1dbfd4572</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3.7 Pipeline Register Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3.7 Pipeline Register Optimization | Checksum: 1bb4a6675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 3 Detail Placement | Checksum: 1bb4a6675</t>
+    <t xml:space="preserve">Phase 3.7 Pipeline Register Optimization | Checksum: 1b2f1805b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 3 Detail Placement | Checksum: 1b2f1805b</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 4 Post Placement Optimization and Clean-Up</t>
@@ -2176,7 +2176,7 @@
     <t xml:space="preserve">Phase 4.1.1 Post Placement Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Post Placement Optimization Initialization | Checksum: 111b052d2</t>
+    <t xml:space="preserve">Post Placement Optimization Initialization | Checksum: 1a3f7ef48</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 4.1.1.1 BUFG Insertion</t>
@@ -2191,46 +2191,40 @@
     <t xml:space="preserve">INFO: [Physopt 32-721] Multithreading enabled for phys_opt_design using a maximum of 8 CPUs</t>
   </si>
   <si>
-    <t xml:space="preserve">INFO: [Physopt 32-619] Estimated Timing Summary | WNS=11.168 | TNS=0.000 |</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 Physical Synthesis Initialization | Checksum: 10d36cfa1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.08 ; elapsed = 00:00:00.02 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14966 ; free virtual = 30230</t>
+    <t xml:space="preserve">INFO: [Physopt 32-619] Estimated Timing Summary | WNS=11.431 | TNS=0.000 |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 1 Physical Synthesis Initialization | Checksum: 152663c00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.1 ; elapsed = 00:00:00.02 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14941 ; free virtual = 34074</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Place 46-56] BUFG insertion identified 0 candidate nets. Inserted BUFG: 0, Replicated BUFG Driver: 0, Skipped due to Placement/Routing Conflicts: 0, Skipped due to Timing Degradation: 0, Skipped due to netlist editing failed: 0.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ending Physical Synthesis Task | Checksum: 5ebee154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.09 ; elapsed = 00:00:00.02 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14966 ; free virtual = 30230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4.1.1.1 BUFG Insertion | Checksum: 111b052d2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:06 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14966 ; free virtual = 30230</t>
+    <t xml:space="preserve">Ending Physical Synthesis Task | Checksum: 1000eaf7e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4.1.1.1 BUFG Insertion | Checksum: 1a3f7ef48</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 4.1.1.2 Post Placement Timing Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">INFO: [Place 30-746] Post Placement Timing Summary WNS=11.168. For the most accurate timing information please run report_timing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4.1.1.2 Post Placement Timing Optimization | Checksum: e8637e2b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4.1 Post Commit Optimization | Checksum: e8637e2b</t>
+    <t xml:space="preserve">INFO: [Place 30-746] Post Placement Timing Summary WNS=11.431. For the most accurate timing information please run report_timing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4.1.1.2 Post Placement Timing Optimization | Checksum: 12af23bcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4.1 Post Commit Optimization | Checksum: 12af23bcc</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 4.2 Post Placement Cleanup</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 4.2 Post Placement Cleanup | Checksum: e8637e2b</t>
+    <t xml:space="preserve">Phase 4.2 Post Placement Cleanup | Checksum: 12af23bcc</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 4.3 Placer Reporting</t>
@@ -2266,25 +2260,22 @@
     <t xml:space="preserve">|       West|                1x1|                1x1|</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 4.3.1 Print Estimated Congestion | Checksum: e8637e2b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:07 ; elapsed = 00:00:02 . Memory (MB): peak = 3635.223 ; gain = 39.043 ; free physical = 14966 ; free virtual = 30230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4.3 Placer Reporting | Checksum: e8637e2b</t>
+    <t xml:space="preserve">Phase 4.3.1 Print Estimated Congestion | Checksum: 12af23bcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4.3 Placer Reporting | Checksum: 12af23bcc</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 4.4 Final Placement Cleanup</t>
   </si>
   <si>
-    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14966 ; free virtual = 30230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4 Post Placement Optimization and Clean-Up | Checksum: ee637658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ending Placer Task | Checksum: 4a862fea</t>
+    <t xml:space="preserve">Netlist sorting complete. Time (s): cpu = 00:00:00 ; elapsed = 00:00:00 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14941 ; free virtual = 34074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4 Post Placement Optimization and Clean-Up | Checksum: 11aca08b0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ending Placer Task | Checksum: ce5a134b</t>
   </si>
   <si>
     <t xml:space="preserve">30 Infos, 0 Warnings, 0 Critical Warnings and 0 Errors encountered.</t>
@@ -2305,13 +2296,13 @@
     <t xml:space="preserve"># report_io                              -file "${RESULTS_DIR}/impl/${PROJECT_NAME}_io.rpt"</t>
   </si>
   <si>
-    <t xml:space="preserve">report_io: Time (s): cpu = 00:00:00.09 ; elapsed = 00:00:00.15 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14958 ; free virtual = 30221</t>
+    <t xml:space="preserve">report_io: Time (s): cpu = 00:00:00.09 ; elapsed = 00:00:00.15 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14921 ; free virtual = 34054</t>
   </si>
   <si>
     <t xml:space="preserve"># report_control_sets      -verbose      -file "${RESULTS_DIR}/impl/${PROJECT_NAME}_control_sets.rpt"</t>
   </si>
   <si>
-    <t xml:space="preserve">report_control_sets: Time (s): cpu = 00:00:00 ; elapsed = 00:00:00.06 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14958 ; free virtual = 30222</t>
+    <t xml:space="preserve">report_control_sets: Time (s): cpu = 00:00:00 ; elapsed = 00:00:00.06 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14919 ; free virtual = 34052</t>
   </si>
   <si>
     <t xml:space="preserve"># report_clock_utilization               -file "${RESULTS_DIR}/impl/${PROJECT_NAME}_clock_utilization.rpt"</t>
@@ -2335,16 +2326,16 @@
     <t xml:space="preserve">Phase 1 Build RT Design</t>
   </si>
   <si>
-    <t xml:space="preserve">Checksum: PlaceDB: 8b8b9d8 ConstDB: 0 ShapeSum: 2bd40322 RouteDB: 15f972f0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post Restoration Checksum: NetGraph: 3cb18b19 | NumContArr: 6d06b416 | Constraints: c2a8fa9d | Timing: c2a8fa9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 Build RT Design | Checksum: 22f0a3469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:21 ; elapsed = 00:00:19 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14987 ; free virtual = 30251</t>
+    <t xml:space="preserve">Checksum: PlaceDB: 5d24a96f ConstDB: 0 ShapeSum: 5b3bf6ec RouteDB: 15f972f0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post Restoration Checksum: NetGraph: bf4fac3d | NumContArr: f92f1dd7 | Constraints: c2a8fa9d | Timing: c2a8fa9d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 1 Build RT Design | Checksum: 33dd0bf4e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:21 ; elapsed = 00:00:19 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14944 ; free virtual = 34077</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2 Router Initialization</t>
@@ -2353,13 +2344,13 @@
     <t xml:space="preserve">Phase 2.1 Fix Topology Constraints</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.1 Fix Topology Constraints | Checksum: 22f0a3469</t>
+    <t xml:space="preserve">Phase 2.1 Fix Topology Constraints | Checksum: 33dd0bf4e</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.2 Pre Route Cleanup</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.2 Pre Route Cleanup | Checksum: 22f0a3469</t>
+    <t xml:space="preserve">Phase 2.2 Pre Route Cleanup | Checksum: 33dd0bf4e</t>
   </si>
   <si>
     <t xml:space="preserve"> Number of Nodes with overlaps = 0</t>
@@ -2368,13 +2359,13 @@
     <t xml:space="preserve">Phase 2.3 Update Timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.3 Update Timing | Checksum: 30f0458dd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:22 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14987 ; free virtual = 30251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.172 | TNS=0.000  | WHS=-0.148 | THS=-10.855|</t>
+    <t xml:space="preserve">Phase 2.3 Update Timing | Checksum: 193f319a4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:22 ; elapsed = 00:00:19 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14943 ; free virtual = 34076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.511 | TNS=0.000  | WHS=-0.148 | THS=-10.816|</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.4 Update Timing for Bus Skew</t>
@@ -2383,22 +2374,25 @@
     <t xml:space="preserve">Phase 2.4.1 Update Timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.4.1 Update Timing | Checksum: 2d547deb3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:23 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14987 ; free virtual = 30251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.172 | TNS=0.000  | WHS=0.048  | THS=0.000  |</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 2.4 Update Timing for Bus Skew | Checksum: 28d7577ea</t>
+    <t xml:space="preserve">Phase 2.4.1 Update Timing | Checksum: 1c16166a8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:22 ; elapsed = 00:00:19 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14945 ; free virtual = 34077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.511 | TNS=0.000  | WHS=0.086  | THS=0.000  |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 2.4 Update Timing for Bus Skew | Checksum: 1cf3f21db</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:22 ; elapsed = 00:00:19 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14945 ; free virtual = 34078</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 2.5 Soft Constraint Pins - Fast Budgeting</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2.5 Soft Constraint Pins - Fast Budgeting | Checksum: 28d7577ea</t>
+    <t xml:space="preserve">Phase 2.5 Soft Constraint Pins - Fast Budgeting | Checksum: 1cf3f21db</t>
   </si>
   <si>
     <t xml:space="preserve">Router Utilization Summary</t>
@@ -2419,13 +2413,13 @@
     <t xml:space="preserve">  Run report_route_status for detailed report.</t>
   </si>
   <si>
-    <t xml:space="preserve">  Number of Failed Nets               = 506</t>
+    <t xml:space="preserve">  Number of Failed Nets               = 500</t>
   </si>
   <si>
     <t xml:space="preserve">    (Failed Nets is the sum of unrouted and partially routed nets)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Number of Unrouted Nets             = 506</t>
+    <t xml:space="preserve">  Number of Unrouted Nets             = 500</t>
   </si>
   <si>
     <t xml:space="preserve">  Number of Partially Routed Nets     = 0</t>
@@ -2434,13 +2428,16 @@
     <t xml:space="preserve">  Number of Node Overlaps             = 0</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 2 Router Initialization | Checksum: 29b39cd81</t>
+    <t xml:space="preserve">Phase 2 Router Initialization | Checksum: 1fe3e7a69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:23 ; elapsed = 00:00:19 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14944 ; free virtual = 34077</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3 Global Routing</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 3 Global Routing | Checksum: 29b39cd81</t>
+    <t xml:space="preserve">Phase 3 Global Routing | Checksum: 1fe3e7a69</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 4 Initial Routing</t>
@@ -2449,16 +2446,10 @@
     <t xml:space="preserve">Phase 4.1 Initial Net Routing Pass</t>
   </si>
   <si>
-    <t xml:space="preserve">WARNING: [Route 35-3387] High violations detected on bus-skew constraints. This can potentially cause WNS degradation and routing congestion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolution: Please review the set_bus_skew constraints.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4.1 Initial Net Routing Pass | Checksum: 29b81f9b7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 4 Initial Routing | Checksum: 29b81f9b7</t>
+    <t xml:space="preserve">Phase 4.1 Initial Net Routing Pass | Checksum: 2702a7522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 4 Initial Routing | Checksum: 2702a7522</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 5 Rip-up And Reroute</t>
@@ -2467,25 +2458,16 @@
     <t xml:space="preserve">Phase 5.1 Global Iteration 0</t>
   </si>
   <si>
-    <t xml:space="preserve"> Number of Nodes with overlaps = 40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.393 | TNS=0.000  | WHS=N/A    | THS=N/A    |</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 5.1 Global Iteration 0 | Checksum: 198bed09d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:24 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14987 ; free virtual = 30251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 5.2 Global Iteration 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 5.2 Global Iteration 1 | Checksum: 2000bd7dd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 5 Rip-up And Reroute | Checksum: 2000bd7dd</t>
+    <t xml:space="preserve"> Number of Nodes with overlaps = 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.048 | TNS=0.000  | WHS=N/A    | THS=N/A    |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 5.1 Global Iteration 0 | Checksum: 218541c8a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 5 Rip-up And Reroute | Checksum: 218541c8a</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 6 Delay and Skew Optimization</t>
@@ -2494,16 +2476,25 @@
     <t xml:space="preserve">Phase 6.1 Delay CleanUp</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 6.1 Delay CleanUp | Checksum: 2000bd7dd</t>
+    <t xml:space="preserve">Phase 6.1.1 Update Timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 6.1.1 Update Timing | Checksum: 14e1ebfd4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.066 | TNS=0.000  | WHS=N/A    | THS=N/A    |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 6.1 Delay CleanUp | Checksum: 12f086780</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 6.2 Clock Skew Optimization</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 6.2 Clock Skew Optimization | Checksum: 2000bd7dd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 6 Delay and Skew Optimization | Checksum: 2000bd7dd</t>
+    <t xml:space="preserve">Phase 6.2 Clock Skew Optimization | Checksum: 12f086780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 6 Delay and Skew Optimization | Checksum: 12f086780</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 7 Post Hold Fix</t>
@@ -2512,22 +2503,22 @@
     <t xml:space="preserve">Phase 7.1 Hold Fix Iter</t>
   </si>
   <si>
-    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.407 | TNS=0.000  | WHS=0.121  | THS=0.000  |</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 7.1 Hold Fix Iter | Checksum: 177f7e8a3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 7 Post Hold Fix | Checksum: 177f7e8a3</t>
+    <t xml:space="preserve">INFO: [Route 35-416] Intermediate Timing Summary | WNS=11.066 | TNS=0.000  | WHS=0.087  | THS=0.000  |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 7.1 Hold Fix Iter | Checksum: 1c8ce97e3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 7 Post Hold Fix | Checksum: 1c8ce97e3</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 8 Route finalize</t>
   </si>
   <si>
-    <t xml:space="preserve">  Global Vertical Routing Utilization    = 0.127317 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Global Horizontal Routing Utilization  = 0.118915 %</t>
+    <t xml:space="preserve">  Global Vertical Routing Utilization    = 0.131666 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Global Horizontal Routing Utilization  = 0.126014 %</t>
   </si>
   <si>
     <t xml:space="preserve">  Number of Failed Nets               = 0</t>
@@ -2536,7 +2527,7 @@
     <t xml:space="preserve">  Number of Unrouted Nets             = 0</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 8 Route finalize | Checksum: 177f7e8a3</t>
+    <t xml:space="preserve">Phase 8 Route finalize | Checksum: 1c8ce97e3</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 9 Verifying routed nets</t>
@@ -2545,61 +2536,67 @@
     <t xml:space="preserve"> Verification completed successfully</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 9 Verifying routed nets | Checksum: 177f7e8a3</t>
+    <t xml:space="preserve">Phase 9 Verifying routed nets | Checksum: 1c8ce97e3</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 10 Depositing Routes</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 10 Depositing Routes | Checksum: 1796b7b36</t>
+    <t xml:space="preserve">Phase 10 Depositing Routes | Checksum: 1de62c77d</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 11 Post Process Routing</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 11 Post Process Routing | Checksum: 1796b7b36</t>
+    <t xml:space="preserve">Phase 11 Post Process Routing | Checksum: 1de62c77d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:23 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14944 ; free virtual = 34077</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 12 Post Router Timing</t>
   </si>
   <si>
-    <t xml:space="preserve">INFO: [Route 35-57] Estimated Timing Summary | WNS=11.407 | TNS=0.000  | WHS=0.121  | THS=0.000  |</t>
+    <t xml:space="preserve">INFO: [Route 35-57] Estimated Timing Summary | WNS=11.066 | TNS=0.000  | WHS=0.087  | THS=0.000  |</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Route 35-327] The final timing numbers are based on the router estimated timing analysis. For a complete and accurate timing signoff, please run report_timing_summary.</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 12 Post Router Timing | Checksum: 1796b7b36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Elapsed time in route_design: 20.03 secs</t>
+    <t xml:space="preserve">Phase 12 Post Router Timing | Checksum: 1de62c77d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:23 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14944 ; free virtual = 34076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Elapsed time in route_design: 19.49 secs</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 13 Post-Route Event Processing</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 13 Post-Route Event Processing | Checksum: 12dfc266a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:24 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14987 ; free virtual = 30250</t>
+    <t xml:space="preserve">Phase 13 Post-Route Event Processing | Checksum: 197dba0ee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time (s): cpu = 00:00:23 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14943 ; free virtual = 34076</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Route 35-16] Router Completed Successfully</t>
   </si>
   <si>
-    <t xml:space="preserve">Ending Routing Task | Checksum: 12dfc266a</t>
+    <t xml:space="preserve">Ending Routing Task | Checksum: 197dba0ee</t>
   </si>
   <si>
     <t xml:space="preserve">Routing Is Done.</t>
   </si>
   <si>
-    <t xml:space="preserve">12 Infos, 1 Warnings, 0 Critical Warnings and 0 Errors encountered.</t>
+    <t xml:space="preserve">12 Infos, 0 Warnings, 0 Critical Warnings and 0 Errors encountered.</t>
   </si>
   <si>
     <t xml:space="preserve">route_design completed successfully</t>
   </si>
   <si>
-    <t xml:space="preserve">route_design: Time (s): cpu = 00:00:24 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14987 ; free virtual = 30250</t>
+    <t xml:space="preserve">route_design: Time (s): cpu = 00:00:24 ; elapsed = 00:00:20 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14943 ; free virtual = 34076</t>
   </si>
   <si>
     <t xml:space="preserve"># phys_opt_design -directive "default"</t>
@@ -2617,10 +2614,10 @@
     <t xml:space="preserve">Starting Initial Update Timing Task</t>
   </si>
   <si>
-    <t xml:space="preserve">Time (s): cpu = 00:00:00.23 ; elapsed = 00:00:00.05 . Memory (MB): peak = 3635.223 ; gain = 0.000 ; free physical = 14985 ; free virtual = 30249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO: [Vivado_Tcl 4-2279] Estimated Timing Summary | WNS= 11.409 | TNS= 0.000 |</t>
+    <t xml:space="preserve">Time (s): cpu = 00:00:00.21 ; elapsed = 00:00:00.05 . Memory (MB): peak = 3635.602 ; gain = 0.000 ; free physical = 14943 ; free virtual = 34076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Vivado_Tcl 4-2279] Estimated Timing Summary | WNS= 11.037 | TNS= 0.000 |</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Vivado_Tcl 4-383] Design worst setup slack (WNS) is greater than or equal to 0.000 ns. All physical synthesis setup optimizations will be skipped.</t>
@@ -2836,7 +2833,7 @@
     <t xml:space="preserve">    -------      -------  ---------------------  -------------------      -------      -------  ---------------------  -------------------     --------     --------  ----------------------  --------------------</t>
   </si>
   <si>
-    <t xml:space="preserve">     11.409        0.000                      0                  812        0.122        0.000                      0                  769        3.000        0.000                       0                   359</t>
+    <t xml:space="preserve">     11.037        0.000                      0                  812        0.088        0.000                      0                  769        3.000        0.000                       0                   359</t>
   </si>
   <si>
     <t xml:space="preserve">All user specified timing constraints are met.</t>
@@ -2881,10 +2878,10 @@
     <t xml:space="preserve">PAD_I_CLK                                                                                                                                                               3.000        0.000                       0                     1</t>
   </si>
   <si>
-    <t xml:space="preserve">  clk_out1_clk_wiz_0       14.041        0.000                      0                  434        0.122        0.000                      0                  429        9.500        0.000                       0                   280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  clk_out2_clk_wiz_0       11.409        0.000                      0                   80        0.122        0.000                      0                   75        7.192        0.000                       0                    75</t>
+    <t xml:space="preserve">  clk_out1_clk_wiz_0       14.041        0.000                      0                  434        0.088        0.000                      0                  429        9.500        0.000                       0                   280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  clk_out2_clk_wiz_0       11.037        0.000                      0                   80        0.115        0.000                      0                   75        7.192        0.000                       0                    75</t>
   </si>
   <si>
     <t xml:space="preserve">  clkfbout_clk_wiz_0                                                                                                                                                    7.845        0.000                       0                     3</t>
@@ -2899,13 +2896,13 @@
     <t xml:space="preserve">----------          --------                -------      -------  ---------------------  -------------------      -------      -------  ---------------------  -------------------</t>
   </si>
   <si>
-    <t xml:space="preserve">input port clock    clk_out1_clk_wiz_0       17.933        0.000                      0                    3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clk_out2_clk_wiz_0  clk_out1_clk_wiz_0       13.604        0.000                      0                    9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clk_out1_clk_wiz_0  clk_out2_clk_wiz_0       13.461        0.000                      0                   21</t>
+    <t xml:space="preserve">input port clock    clk_out1_clk_wiz_0       17.934        0.000                      0                    3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clk_out2_clk_wiz_0  clk_out1_clk_wiz_0       13.829        0.000                      0                    9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clk_out1_clk_wiz_0  clk_out2_clk_wiz_0       13.655        0.000                      0                   21</t>
   </si>
   <si>
     <t xml:space="preserve">| Other Path Groups Table</t>
@@ -2920,10 +2917,10 @@
     <t xml:space="preserve">----------          ----------          --------                -------      -------  ---------------------  -------------------      -------      -------  ---------------------  -------------------</t>
   </si>
   <si>
-    <t xml:space="preserve">**async_default**   clk_out1_clk_wiz_0  clk_out1_clk_wiz_0       16.985        0.000                      0                  230        0.424        0.000                      0                  230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**async_default**   clk_out2_clk_wiz_0  clk_out2_clk_wiz_0       12.773        0.000                      0                   35        0.411        0.000                      0                   35</t>
+    <t xml:space="preserve">**async_default**   clk_out1_clk_wiz_0  clk_out1_clk_wiz_0       16.153        0.000                      0                  230        0.430        0.000                      0                  230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**async_default**   clk_out2_clk_wiz_0  clk_out2_clk_wiz_0       12.135        0.000                      0                   35        0.456        0.000                      0                   35</t>
   </si>
   <si>
     <t xml:space="preserve"># report_bus_skew                                     -file "${RESULTS_DIR}/impl/${PROJECT_NAME}_bus_skew.rpt"</t>
@@ -3041,7 +3038,7 @@
     <t xml:space="preserve">write_bitstream completed successfully</t>
   </si>
   <si>
-    <t xml:space="preserve">write_bitstream: Time (s): cpu = 00:00:13 ; elapsed = 00:00:26 . Memory (MB): peak = 3643.227 ; gain = 0.000 ; free physical = 14965 ; free virtual = 30229</t>
+    <t xml:space="preserve">write_bitstream: Time (s): cpu = 00:00:13 ; elapsed = 00:00:26 . Memory (MB): peak = 3643.605 ; gain = 0.000 ; free physical = 14913 ; free virtual = 34046</t>
   </si>
   <si>
     <t xml:space="preserve"># if {![file exists $file]} {</t>
@@ -3051,6 +3048,9 @@
   </si>
   <si>
     <t xml:space="preserve">#     file rename -force "$CURRENT_DIR/vivado.log" "$RESULTS_DIR/${PROJECT_NAME}.log"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO: [Common 17-206] Exiting Vivado at Thu Apr  9 14:13:22 2026...</t>
   </si>
   <si>
     <t xml:space="preserve">INFO: [Common 17-206] Exiting Vivado at Wed Mar 25 22:45:59 2026...</t>
@@ -4249,7 +4249,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="18" operator="between" id="{00C200BC-0095-4715-9415-002500780087}">
+          <x14:cfRule type="cellIs" priority="18" operator="between" id="{0079003D-002E-4DB2-B9F3-003B00FE0059}">
             <xm:f>98%</xm:f>
             <xm:f>100%</xm:f>
             <x14:dxf>
@@ -4264,7 +4264,7 @@
           <xm:sqref>H10:H17</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="between" id="{0065001C-00A6-447F-9384-001500A000EE}">
+          <x14:cfRule type="cellIs" priority="1" operator="between" id="{00A400FE-007E-433D-8780-0015008800BB}">
             <xm:f>99.99%</xm:f>
             <xm:f>100%</xm:f>
             <x14:dxf>
@@ -4279,7 +4279,7 @@
           <xm:sqref>H3:L9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="between" id="{00A20095-0096-488A-85C7-00F7009F0039}">
+          <x14:cfRule type="cellIs" priority="2" operator="between" id="{006A0061-0034-4A1C-9BAC-002600310073}">
             <xm:f>90%</xm:f>
             <xm:f>99.99%</xm:f>
             <x14:dxf>
@@ -4294,7 +4294,7 @@
           <xm:sqref>H3:L9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="between" id="{0020001A-0093-43FE-9017-008A000A000D}">
+          <x14:cfRule type="cellIs" priority="3" operator="between" id="{00B0009C-0014-4C8F-99E4-001F009300CF}">
             <xm:f>80%</xm:f>
             <xm:f>90%</xm:f>
             <x14:dxf>
@@ -4309,7 +4309,7 @@
           <xm:sqref>H3:L9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="between" id="{00BB00E1-0061-43C2-83A8-009300C900F0}">
+          <x14:cfRule type="cellIs" priority="4" operator="between" id="{00AF00C4-0095-4D97-B2A4-005600BC009F}">
             <xm:f>0.1%</xm:f>
             <xm:f>80%</xm:f>
             <x14:dxf>
@@ -11092,7 +11092,7 @@
         <v/>
       </c>
       <c r="C680" s="22" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D680" s="22"/>
     </row>
@@ -11102,7 +11102,7 @@
         <v/>
       </c>
       <c r="C681" s="22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D681" s="22"/>
     </row>
@@ -11120,7 +11120,7 @@
         <v/>
       </c>
       <c r="C683" s="22" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D683" s="22"/>
     </row>
@@ -11138,7 +11138,7 @@
         <v/>
       </c>
       <c r="C685" s="22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D685" s="22"/>
     </row>
@@ -11148,7 +11148,7 @@
         <v>INFO</v>
       </c>
       <c r="C686" s="22" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D686" s="22"/>
     </row>
@@ -11158,7 +11158,7 @@
         <v>INFO</v>
       </c>
       <c r="C687" s="22" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D687" s="22"/>
     </row>
@@ -11168,7 +11168,7 @@
         <v>INFO</v>
       </c>
       <c r="C688" s="22" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D688" s="22"/>
     </row>
@@ -11188,7 +11188,7 @@
         <v>INFO</v>
       </c>
       <c r="C690" s="22" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D690" s="22"/>
     </row>
@@ -11198,7 +11198,7 @@
         <v/>
       </c>
       <c r="C691" s="22" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D691" s="22"/>
     </row>
@@ -11216,7 +11216,7 @@
         <v/>
       </c>
       <c r="C693" s="22" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D693" s="22"/>
     </row>
@@ -11226,7 +11226,7 @@
         <v/>
       </c>
       <c r="C694" s="22" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D694" s="22"/>
     </row>
@@ -11236,7 +11236,7 @@
         <v>INFO</v>
       </c>
       <c r="C695" s="22" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D695" s="22"/>
     </row>
@@ -11246,7 +11246,7 @@
         <v>INFO</v>
       </c>
       <c r="C696" s="22" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D696" s="22"/>
     </row>
@@ -11264,7 +11264,7 @@
         <v/>
       </c>
       <c r="C698" s="22" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D698" s="22"/>
     </row>
@@ -11284,7 +11284,7 @@
         <v/>
       </c>
       <c r="C700" s="22" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D700" s="22"/>
     </row>
@@ -11302,7 +11302,7 @@
         <v/>
       </c>
       <c r="C702" s="22" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D702" s="22"/>
     </row>
@@ -11312,7 +11312,7 @@
         <v/>
       </c>
       <c r="C703" s="22" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D703" s="22"/>
     </row>
@@ -11322,7 +11322,7 @@
         <v>INFO</v>
       </c>
       <c r="C704" s="22" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D704" s="22"/>
     </row>
@@ -11340,7 +11340,7 @@
         <v/>
       </c>
       <c r="C706" s="22" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D706" s="22"/>
     </row>
@@ -11350,7 +11350,7 @@
         <v>INFO</v>
       </c>
       <c r="C707" s="22" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D707" s="22"/>
     </row>
@@ -11360,7 +11360,7 @@
         <v/>
       </c>
       <c r="C708" s="22" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D708" s="22"/>
     </row>
@@ -11370,7 +11370,7 @@
         <v>INFO</v>
       </c>
       <c r="C709" s="22" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D709" s="22"/>
     </row>
@@ -11380,7 +11380,7 @@
         <v/>
       </c>
       <c r="C710" s="22" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D710" s="22"/>
     </row>
@@ -11390,7 +11390,7 @@
         <v/>
       </c>
       <c r="C711" s="22" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D711" s="22"/>
     </row>
@@ -11408,7 +11408,7 @@
         <v/>
       </c>
       <c r="C713" s="22" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="D713" s="22"/>
     </row>
@@ -11418,7 +11418,7 @@
         <v/>
       </c>
       <c r="C714" s="22" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D714" s="22"/>
     </row>
@@ -11428,7 +11428,7 @@
         <v>INFO</v>
       </c>
       <c r="C715" s="22" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D715" s="22"/>
     </row>
@@ -11438,7 +11438,7 @@
         <v>INFO</v>
       </c>
       <c r="C716" s="22" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D716" s="22"/>
     </row>
@@ -11456,7 +11456,7 @@
         <v/>
       </c>
       <c r="C718" s="22" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D718" s="22"/>
     </row>
@@ -11466,7 +11466,7 @@
         <v/>
       </c>
       <c r="C719" s="22" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D719" s="22"/>
     </row>
@@ -11484,7 +11484,7 @@
         <v/>
       </c>
       <c r="C721" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D721" s="22"/>
     </row>
@@ -11494,7 +11494,7 @@
         <v/>
       </c>
       <c r="C722" s="22" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D722" s="22"/>
     </row>
@@ -11504,7 +11504,7 @@
         <v>INFO</v>
       </c>
       <c r="C723" s="22" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D723" s="22"/>
     </row>
@@ -11522,7 +11522,7 @@
         <v/>
       </c>
       <c r="C725" s="22" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D725" s="22"/>
     </row>
@@ -11532,7 +11532,7 @@
         <v>INFO</v>
       </c>
       <c r="C726" s="22" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D726" s="22"/>
     </row>
@@ -11542,7 +11542,7 @@
         <v/>
       </c>
       <c r="C727" s="22" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D727" s="22"/>
     </row>
@@ -11560,7 +11560,7 @@
         <v/>
       </c>
       <c r="C729" s="22" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="D729" s="22"/>
     </row>
@@ -11570,7 +11570,7 @@
         <v/>
       </c>
       <c r="C730" s="22" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D730" s="22"/>
     </row>
@@ -11580,7 +11580,7 @@
         <v>INFO</v>
       </c>
       <c r="C731" s="22" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D731" s="22"/>
     </row>
@@ -11598,7 +11598,7 @@
         <v/>
       </c>
       <c r="C733" s="22" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D733" s="22"/>
     </row>
@@ -11608,7 +11608,7 @@
         <v/>
       </c>
       <c r="C734" s="22" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D734" s="22"/>
     </row>
@@ -11626,7 +11626,7 @@
         <v/>
       </c>
       <c r="C736" s="22" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D736" s="22"/>
     </row>
@@ -11636,7 +11636,7 @@
         <v/>
       </c>
       <c r="C737" s="22" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D737" s="22"/>
     </row>
@@ -11646,7 +11646,7 @@
         <v>INFO</v>
       </c>
       <c r="C738" s="22" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D738" s="22"/>
     </row>
@@ -11664,7 +11664,7 @@
         <v/>
       </c>
       <c r="C740" s="22" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D740" s="22"/>
     </row>
@@ -11682,7 +11682,7 @@
         <v/>
       </c>
       <c r="C742" s="22" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D742" s="22"/>
     </row>
@@ -11692,7 +11692,7 @@
         <v/>
       </c>
       <c r="C743" s="22" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D743" s="22"/>
     </row>
@@ -11710,7 +11710,7 @@
         <v/>
       </c>
       <c r="C745" s="22" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D745" s="22"/>
     </row>
@@ -11728,7 +11728,7 @@
         <v/>
       </c>
       <c r="C747" s="22" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D747" s="22"/>
     </row>
@@ -11746,7 +11746,7 @@
         <v/>
       </c>
       <c r="C749" s="22" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D749" s="22"/>
     </row>
@@ -11764,7 +11764,7 @@
         <v/>
       </c>
       <c r="C751" s="22" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D751" s="22"/>
     </row>
@@ -11774,7 +11774,7 @@
         <v/>
       </c>
       <c r="C752" s="22" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D752" s="22"/>
     </row>
@@ -11792,7 +11792,7 @@
         <v/>
       </c>
       <c r="C754" s="22" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D754" s="22"/>
     </row>
@@ -11802,7 +11802,7 @@
         <v/>
       </c>
       <c r="C755" s="22" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="D755" s="22"/>
     </row>
@@ -11820,7 +11820,7 @@
         <v/>
       </c>
       <c r="C757" s="22" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D757" s="22"/>
     </row>
@@ -11830,7 +11830,7 @@
         <v/>
       </c>
       <c r="C758" s="22" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D758" s="22"/>
     </row>
@@ -11840,7 +11840,7 @@
         <v/>
       </c>
       <c r="C759" s="22" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D759" s="22"/>
     </row>
@@ -11866,7 +11866,7 @@
         <v/>
       </c>
       <c r="C762" s="22" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D762" s="22"/>
     </row>
@@ -11876,7 +11876,7 @@
         <v/>
       </c>
       <c r="C763" s="22" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D763" s="22"/>
     </row>
@@ -11886,7 +11886,7 @@
         <v/>
       </c>
       <c r="C764" s="22" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D764" s="22"/>
     </row>
@@ -11896,7 +11896,7 @@
         <v/>
       </c>
       <c r="C765" s="22" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="D765" s="22"/>
     </row>
@@ -11906,7 +11906,7 @@
         <v/>
       </c>
       <c r="C766" s="22" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="D766" s="22"/>
     </row>
@@ -11916,7 +11916,7 @@
         <v/>
       </c>
       <c r="C767" s="22" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D767" s="22"/>
     </row>
@@ -11926,7 +11926,7 @@
         <v/>
       </c>
       <c r="C768" s="22" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D768" s="22"/>
     </row>
@@ -11936,7 +11936,7 @@
         <v/>
       </c>
       <c r="C769" s="22" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D769" s="22"/>
     </row>
@@ -11946,7 +11946,7 @@
         <v/>
       </c>
       <c r="C770" s="22" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D770" s="22"/>
     </row>
@@ -11956,7 +11956,7 @@
         <v/>
       </c>
       <c r="C771" s="22" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="D771" s="22"/>
     </row>
@@ -11982,7 +11982,7 @@
         <v/>
       </c>
       <c r="C774" s="22" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D774" s="22"/>
     </row>
@@ -12000,7 +12000,7 @@
         <v/>
       </c>
       <c r="C776" s="22" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D776" s="22"/>
     </row>
@@ -12018,7 +12018,7 @@
         <v/>
       </c>
       <c r="C778" s="22" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D778" s="22"/>
     </row>
@@ -12028,7 +12028,7 @@
         <v>INFO</v>
       </c>
       <c r="C779" s="22" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D779" s="22"/>
     </row>
@@ -12038,7 +12038,7 @@
         <v/>
       </c>
       <c r="C780" s="22" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D780" s="22"/>
     </row>
@@ -12056,7 +12056,7 @@
         <v/>
       </c>
       <c r="C782" s="22" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="D782" s="22"/>
     </row>
@@ -12074,7 +12074,7 @@
         <v/>
       </c>
       <c r="C784" s="22" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D784" s="22"/>
     </row>
@@ -12084,7 +12084,7 @@
         <v/>
       </c>
       <c r="C785" s="22" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D785" s="22"/>
     </row>
@@ -12102,7 +12102,7 @@
         <v/>
       </c>
       <c r="C787" s="22" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D787" s="22"/>
     </row>
@@ -12112,7 +12112,7 @@
         <v/>
       </c>
       <c r="C788" s="22" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D788" s="22"/>
     </row>
@@ -12122,7 +12122,7 @@
         <v>INFO</v>
       </c>
       <c r="C789" s="22" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D789" s="22"/>
     </row>
@@ -12132,7 +12132,7 @@
         <v/>
       </c>
       <c r="C790" s="22" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D790" s="22"/>
     </row>
@@ -12142,7 +12142,7 @@
         <v/>
       </c>
       <c r="C791" s="22" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D791" s="22"/>
     </row>
@@ -12152,7 +12152,7 @@
         <v/>
       </c>
       <c r="C792" s="22" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D792" s="22"/>
     </row>
@@ -12162,7 +12162,7 @@
         <v/>
       </c>
       <c r="C793" s="22" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D793" s="22"/>
     </row>
@@ -12192,7 +12192,7 @@
         <v>INFO</v>
       </c>
       <c r="C796" s="22" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D796" s="22"/>
     </row>
@@ -12212,7 +12212,7 @@
         <v>INFO</v>
       </c>
       <c r="C798" s="22" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D798" s="22"/>
     </row>
@@ -12222,7 +12222,7 @@
         <v>INFO</v>
       </c>
       <c r="C799" s="22" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D799" s="22"/>
     </row>
@@ -12242,7 +12242,7 @@
         <v>INFO</v>
       </c>
       <c r="C801" s="22" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D801" s="22"/>
     </row>
@@ -12252,7 +12252,7 @@
         <v/>
       </c>
       <c r="C802" s="22" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D802" s="22"/>
     </row>
@@ -12272,7 +12272,7 @@
         <v>INFO</v>
       </c>
       <c r="C804" s="22" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D804" s="22"/>
     </row>
@@ -12282,7 +12282,7 @@
         <v>INFO</v>
       </c>
       <c r="C805" s="22" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D805" s="22"/>
     </row>
@@ -12292,7 +12292,7 @@
         <v>INFO</v>
       </c>
       <c r="C806" s="22" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D806" s="22"/>
     </row>
@@ -12310,7 +12310,7 @@
         <v/>
       </c>
       <c r="C808" s="22" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D808" s="22"/>
     </row>
@@ -12328,7 +12328,7 @@
         <v/>
       </c>
       <c r="C810" s="22" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D810" s="22"/>
     </row>
@@ -12346,7 +12346,7 @@
         <v/>
       </c>
       <c r="C812" s="22" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D812" s="22"/>
     </row>
@@ -12356,7 +12356,7 @@
         <v/>
       </c>
       <c r="C813" s="22" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D813" s="22"/>
     </row>
@@ -12366,7 +12366,7 @@
         <v/>
       </c>
       <c r="C814" s="22" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D814" s="22"/>
     </row>
@@ -12384,7 +12384,7 @@
         <v/>
       </c>
       <c r="C816" s="22" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D816" s="22"/>
     </row>
@@ -12412,7 +12412,7 @@
         <v/>
       </c>
       <c r="C819" s="22" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D819" s="22"/>
     </row>
@@ -12422,7 +12422,7 @@
         <v/>
       </c>
       <c r="C820" s="22" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D820" s="22"/>
     </row>
@@ -12440,7 +12440,7 @@
         <v/>
       </c>
       <c r="C822" s="22" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D822" s="22"/>
     </row>
@@ -12458,7 +12458,7 @@
         <v/>
       </c>
       <c r="C824" s="22" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D824" s="22"/>
     </row>
@@ -12468,7 +12468,7 @@
         <v/>
       </c>
       <c r="C825" s="22" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D825" s="22"/>
     </row>
@@ -12486,7 +12486,7 @@
         <v/>
       </c>
       <c r="C827" s="22" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D827" s="22"/>
     </row>
@@ -12504,7 +12504,7 @@
         <v/>
       </c>
       <c r="C829" s="22" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D829" s="22"/>
     </row>
@@ -12514,7 +12514,7 @@
         <v/>
       </c>
       <c r="C830" s="22" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D830" s="22"/>
     </row>
@@ -12532,7 +12532,7 @@
         <v/>
       </c>
       <c r="C832" s="22" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D832" s="22"/>
     </row>
@@ -12542,7 +12542,7 @@
         <v/>
       </c>
       <c r="C833" s="22" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D833" s="22"/>
     </row>
@@ -12560,7 +12560,7 @@
         <v/>
       </c>
       <c r="C835" s="22" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D835" s="22"/>
     </row>
@@ -12578,7 +12578,7 @@
         <v/>
       </c>
       <c r="C837" s="22" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D837" s="22"/>
     </row>
@@ -12596,7 +12596,7 @@
         <v/>
       </c>
       <c r="C839" s="22" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D839" s="22"/>
     </row>
@@ -12606,7 +12606,7 @@
         <v/>
       </c>
       <c r="C840" s="22" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D840" s="22"/>
     </row>
@@ -12624,7 +12624,7 @@
         <v/>
       </c>
       <c r="C842" s="22" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D842" s="22"/>
     </row>
@@ -12642,7 +12642,7 @@
         <v/>
       </c>
       <c r="C844" s="22" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D844" s="22"/>
     </row>
@@ -12652,7 +12652,7 @@
         <v/>
       </c>
       <c r="C845" s="22" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D845" s="22"/>
     </row>
@@ -12670,7 +12670,7 @@
         <v/>
       </c>
       <c r="C847" s="22" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D847" s="22"/>
     </row>
@@ -12688,7 +12688,7 @@
         <v/>
       </c>
       <c r="C849" s="22" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D849" s="22"/>
     </row>
@@ -12698,7 +12698,7 @@
         <v/>
       </c>
       <c r="C850" s="22" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D850" s="22"/>
     </row>
@@ -12716,7 +12716,7 @@
         <v/>
       </c>
       <c r="C852" s="22" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D852" s="22"/>
     </row>
@@ -12734,7 +12734,7 @@
         <v/>
       </c>
       <c r="C854" s="22" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D854" s="22"/>
     </row>
@@ -12744,7 +12744,7 @@
         <v/>
       </c>
       <c r="C855" s="22" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D855" s="22"/>
     </row>
@@ -12762,7 +12762,7 @@
         <v/>
       </c>
       <c r="C857" s="22" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D857" s="22"/>
     </row>
@@ -12780,7 +12780,7 @@
         <v/>
       </c>
       <c r="C859" s="22" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D859" s="22"/>
     </row>
@@ -12798,7 +12798,7 @@
         <v/>
       </c>
       <c r="C861" s="22" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D861" s="22"/>
     </row>
@@ -12808,7 +12808,7 @@
         <v/>
       </c>
       <c r="C862" s="22" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D862" s="22"/>
     </row>
@@ -12826,7 +12826,7 @@
         <v/>
       </c>
       <c r="C864" s="22" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D864" s="22"/>
     </row>
@@ -13850,7 +13850,7 @@
         <v/>
       </c>
       <c r="C973" s="22" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D973" s="22"/>
     </row>
@@ -13860,7 +13860,7 @@
         <v/>
       </c>
       <c r="C974" s="22" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D974" s="22"/>
     </row>
@@ -13878,7 +13878,7 @@
         <v/>
       </c>
       <c r="C976" s="22" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="D976" s="22"/>
     </row>
@@ -13896,7 +13896,7 @@
         <v/>
       </c>
       <c r="C978" s="22" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D978" s="22"/>
     </row>
@@ -13906,7 +13906,7 @@
         <v>INFO</v>
       </c>
       <c r="C979" s="22" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D979" s="22"/>
     </row>
@@ -13916,7 +13916,7 @@
         <v/>
       </c>
       <c r="C980" s="22" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D980" s="22"/>
     </row>
@@ -13934,7 +13934,7 @@
         <v/>
       </c>
       <c r="C982" s="22" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="D982" s="22"/>
     </row>
@@ -13952,7 +13952,7 @@
         <v/>
       </c>
       <c r="C984" s="22" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="D984" s="22"/>
     </row>
@@ -13962,7 +13962,7 @@
         <v/>
       </c>
       <c r="C985" s="22" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D985" s="22"/>
     </row>
@@ -13980,7 +13980,7 @@
         <v/>
       </c>
       <c r="C987" s="22" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="D987" s="22"/>
     </row>
@@ -13998,7 +13998,7 @@
         <v/>
       </c>
       <c r="C989" s="22" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D989" s="22"/>
     </row>
@@ -14008,7 +14008,7 @@
         <v/>
       </c>
       <c r="C990" s="22" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D990" s="22"/>
     </row>
@@ -14026,7 +14026,7 @@
         <v/>
       </c>
       <c r="C992" s="22" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="D992" s="22"/>
     </row>
@@ -14044,7 +14044,7 @@
         <v/>
       </c>
       <c r="C994" s="22" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D994" s="22"/>
     </row>
@@ -14062,7 +14062,7 @@
         <v/>
       </c>
       <c r="C996" s="22" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D996" s="22"/>
     </row>
@@ -14072,7 +14072,7 @@
         <v>INFO</v>
       </c>
       <c r="C997" s="22" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D997" s="22"/>
     </row>
@@ -14082,7 +14082,7 @@
         <v/>
       </c>
       <c r="C998" s="22" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D998" s="22"/>
     </row>
@@ -14092,7 +14092,7 @@
         <v/>
       </c>
       <c r="C999" s="22" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D999" s="22"/>
     </row>
@@ -14102,7 +14102,7 @@
         <v/>
       </c>
       <c r="C1000" s="22" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D1000" s="22"/>
     </row>
@@ -14112,7 +14112,7 @@
         <v/>
       </c>
       <c r="C1001" s="22" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D1001" s="22"/>
     </row>
@@ -14122,7 +14122,7 @@
         <v/>
       </c>
       <c r="C1002" s="22" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D1002" s="22"/>
     </row>
@@ -14132,7 +14132,7 @@
         <v/>
       </c>
       <c r="C1003" s="22" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D1003" s="22"/>
     </row>
@@ -14142,7 +14142,7 @@
         <v/>
       </c>
       <c r="C1004" s="22" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D1004" s="22"/>
     </row>
@@ -14152,7 +14152,7 @@
         <v/>
       </c>
       <c r="C1005" s="22" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D1005" s="22"/>
     </row>
@@ -14162,7 +14162,7 @@
         <v/>
       </c>
       <c r="C1006" s="22" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D1006" s="22"/>
     </row>
@@ -14172,7 +14172,7 @@
         <v/>
       </c>
       <c r="C1007" s="22" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D1007" s="22"/>
     </row>
@@ -14182,7 +14182,7 @@
         <v/>
       </c>
       <c r="C1008" s="22" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D1008" s="22"/>
     </row>
@@ -14192,7 +14192,7 @@
         <v/>
       </c>
       <c r="C1009" s="22" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D1009" s="22"/>
     </row>
@@ -14210,7 +14210,7 @@
         <v/>
       </c>
       <c r="C1011" s="22" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D1011" s="22"/>
     </row>
@@ -14228,7 +14228,7 @@
         <v/>
       </c>
       <c r="C1013" s="22" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="D1013" s="22"/>
     </row>
@@ -14238,7 +14238,7 @@
         <v/>
       </c>
       <c r="C1014" s="22" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D1014" s="22"/>
     </row>
@@ -14256,7 +14256,7 @@
         <v/>
       </c>
       <c r="C1016" s="22" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="D1016" s="22"/>
     </row>
@@ -14274,7 +14274,7 @@
         <v/>
       </c>
       <c r="C1018" s="22" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D1018" s="22"/>
     </row>
@@ -14284,7 +14284,7 @@
         <v/>
       </c>
       <c r="C1019" s="22" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D1019" s="22"/>
     </row>
@@ -14302,7 +14302,7 @@
         <v/>
       </c>
       <c r="C1021" s="22" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="D1021" s="22"/>
     </row>
@@ -14312,7 +14312,7 @@
         <v/>
       </c>
       <c r="C1022" s="22" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D1022" s="22"/>
     </row>
@@ -14330,7 +14330,7 @@
         <v/>
       </c>
       <c r="C1024" s="22" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="D1024" s="22"/>
     </row>
@@ -14340,7 +14340,7 @@
         <v/>
       </c>
       <c r="C1025" s="22" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D1025" s="22"/>
     </row>
@@ -14358,7 +14358,7 @@
         <v/>
       </c>
       <c r="C1027" s="22" t="s">
-        <v>716</v>
+        <v>676</v>
       </c>
       <c r="D1027" s="22"/>
     </row>
@@ -14368,7 +14368,7 @@
         <v/>
       </c>
       <c r="C1028" s="22" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D1028" s="22"/>
     </row>
@@ -14378,7 +14378,7 @@
         <v/>
       </c>
       <c r="C1029" s="22" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D1029" s="22"/>
     </row>
@@ -14388,7 +14388,7 @@
         <v/>
       </c>
       <c r="C1030" s="22" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D1030" s="22"/>
     </row>
@@ -14398,7 +14398,7 @@
         <v/>
       </c>
       <c r="C1031" s="22" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D1031" s="22"/>
     </row>
@@ -14408,7 +14408,7 @@
         <v/>
       </c>
       <c r="C1032" s="22" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D1032" s="22"/>
     </row>
@@ -14418,7 +14418,7 @@
         <v/>
       </c>
       <c r="C1033" s="22" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D1033" s="22"/>
     </row>
@@ -14428,7 +14428,7 @@
         <v/>
       </c>
       <c r="C1034" s="22" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D1034" s="22"/>
     </row>
@@ -14438,7 +14438,7 @@
         <v/>
       </c>
       <c r="C1035" s="22" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D1035" s="22"/>
     </row>
@@ -14448,7 +14448,7 @@
         <v/>
       </c>
       <c r="C1036" s="22" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D1036" s="22"/>
     </row>
@@ -14458,7 +14458,7 @@
         <v/>
       </c>
       <c r="C1037" s="22" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D1037" s="22"/>
     </row>
@@ -14468,7 +14468,7 @@
         <v/>
       </c>
       <c r="C1038" s="22" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D1038" s="22"/>
     </row>
@@ -14478,7 +14478,7 @@
         <v/>
       </c>
       <c r="C1039" s="22" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D1039" s="22"/>
     </row>
@@ -14524,7 +14524,7 @@
         <v/>
       </c>
       <c r="C1044" s="22" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D1044" s="22"/>
     </row>
@@ -14534,7 +14534,7 @@
         <v>INFO</v>
       </c>
       <c r="C1045" s="22" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D1045" s="22"/>
     </row>
@@ -14544,7 +14544,7 @@
         <v>INFO</v>
       </c>
       <c r="C1046" s="22" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D1046" s="22"/>
     </row>
@@ -14562,7 +14562,7 @@
         <v/>
       </c>
       <c r="C1048" s="22" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D1048" s="22"/>
     </row>
@@ -14572,7 +14572,7 @@
         <v/>
       </c>
       <c r="C1049" s="22" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D1049" s="22"/>
     </row>
@@ -14582,7 +14582,7 @@
         <v/>
       </c>
       <c r="C1050" s="22" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D1050" s="22"/>
     </row>
@@ -14592,7 +14592,7 @@
         <v/>
       </c>
       <c r="C1051" s="22" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D1051" s="22"/>
     </row>
@@ -14610,7 +14610,7 @@
         <v/>
       </c>
       <c r="C1053" s="22" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D1053" s="22"/>
     </row>
@@ -14628,7 +14628,7 @@
         <v/>
       </c>
       <c r="C1055" s="22" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D1055" s="22"/>
     </row>
@@ -14646,7 +14646,7 @@
         <v/>
       </c>
       <c r="C1057" s="22" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D1057" s="22"/>
     </row>
@@ -14656,7 +14656,7 @@
         <v/>
       </c>
       <c r="C1058" s="22" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D1058" s="22"/>
     </row>
@@ -14674,7 +14674,7 @@
         <v/>
       </c>
       <c r="C1060" s="22" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D1060" s="22"/>
     </row>
@@ -14692,7 +14692,7 @@
         <v/>
       </c>
       <c r="C1062" s="22" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D1062" s="22"/>
     </row>
@@ -14702,7 +14702,7 @@
         <v/>
       </c>
       <c r="C1063" s="22" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D1063" s="22"/>
     </row>
@@ -14720,7 +14720,7 @@
         <v/>
       </c>
       <c r="C1065" s="22" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D1065" s="22"/>
     </row>
@@ -14730,7 +14730,7 @@
         <v/>
       </c>
       <c r="C1066" s="22" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D1066" s="22"/>
     </row>
@@ -14748,7 +14748,7 @@
         <v/>
       </c>
       <c r="C1068" s="22" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D1068" s="22"/>
     </row>
@@ -14758,7 +14758,7 @@
         <v/>
       </c>
       <c r="C1069" s="22" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D1069" s="22"/>
     </row>
@@ -14776,7 +14776,7 @@
         <v/>
       </c>
       <c r="C1071" s="22" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D1071" s="22"/>
     </row>
@@ -14786,7 +14786,7 @@
         <v>INFO</v>
       </c>
       <c r="C1072" s="22" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D1072" s="22"/>
     </row>
@@ -14812,7 +14812,7 @@
         <v/>
       </c>
       <c r="C1075" s="22" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D1075" s="22"/>
     </row>
@@ -14830,7 +14830,7 @@
         <v/>
       </c>
       <c r="C1077" s="22" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D1077" s="22"/>
     </row>
@@ -14840,7 +14840,7 @@
         <v/>
       </c>
       <c r="C1078" s="22" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D1078" s="22"/>
     </row>
@@ -14858,7 +14858,7 @@
         <v/>
       </c>
       <c r="C1080" s="22" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D1080" s="22"/>
     </row>
@@ -14868,7 +14868,7 @@
         <v>INFO</v>
       </c>
       <c r="C1081" s="22" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D1081" s="22"/>
     </row>
@@ -14886,7 +14886,7 @@
         <v/>
       </c>
       <c r="C1083" s="22" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D1083" s="22"/>
     </row>
@@ -14922,7 +14922,7 @@
         <v/>
       </c>
       <c r="C1087" s="22" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D1087" s="22"/>
     </row>
@@ -14932,7 +14932,7 @@
         <v/>
       </c>
       <c r="C1088" s="22" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D1088" s="22"/>
     </row>
@@ -14968,7 +14968,7 @@
         <v/>
       </c>
       <c r="C1092" s="22" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D1092" s="22"/>
     </row>
@@ -14978,7 +14978,7 @@
         <v/>
       </c>
       <c r="C1093" s="22" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D1093" s="22"/>
     </row>
@@ -14988,7 +14988,7 @@
         <v/>
       </c>
       <c r="C1094" s="22" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D1094" s="22"/>
     </row>
@@ -14998,7 +14998,7 @@
         <v/>
       </c>
       <c r="C1095" s="22" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D1095" s="22"/>
     </row>
@@ -15008,7 +15008,7 @@
         <v/>
       </c>
       <c r="C1096" s="22" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D1096" s="22"/>
     </row>
@@ -15018,7 +15018,7 @@
         <v/>
       </c>
       <c r="C1097" s="22" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D1097" s="22"/>
     </row>
@@ -15028,7 +15028,7 @@
         <v/>
       </c>
       <c r="C1098" s="22" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D1098" s="22"/>
     </row>
@@ -15038,7 +15038,7 @@
         <v/>
       </c>
       <c r="C1099" s="22" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D1099" s="22"/>
     </row>
@@ -15048,7 +15048,7 @@
         <v/>
       </c>
       <c r="C1100" s="22" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D1100" s="22"/>
     </row>
@@ -15058,7 +15058,7 @@
         <v/>
       </c>
       <c r="C1101" s="22" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D1101" s="22"/>
     </row>
@@ -15068,7 +15068,7 @@
         <v/>
       </c>
       <c r="C1102" s="22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D1102" s="22"/>
     </row>
@@ -15086,7 +15086,7 @@
         <v/>
       </c>
       <c r="C1104" s="22" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D1104" s="22"/>
     </row>
@@ -15104,7 +15104,7 @@
         <v/>
       </c>
       <c r="C1106" s="22" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="D1106" s="22"/>
     </row>
@@ -15122,7 +15122,7 @@
         <v/>
       </c>
       <c r="C1108" s="22" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D1108" s="22"/>
     </row>
@@ -15132,7 +15132,7 @@
         <v/>
       </c>
       <c r="C1109" s="22" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D1109" s="22"/>
     </row>
@@ -15150,7 +15150,7 @@
         <v/>
       </c>
       <c r="C1111" s="22" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="D1111" s="22"/>
     </row>
@@ -15168,7 +15168,7 @@
         <v/>
       </c>
       <c r="C1113" s="22" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D1113" s="22"/>
     </row>
@@ -15186,30 +15186,26 @@
         <v/>
       </c>
       <c r="C1115" s="22" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D1115" s="22"/>
     </row>
     <row r="1116">
       <c r="B1116" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>WARNING</v>
+        <v/>
       </c>
       <c r="C1116" s="22" t="s">
-        <v>776</v>
-      </c>
-      <c r="D1116" s="22" t="s">
-        <v>485</v>
-      </c>
+        <v>775</v>
+      </c>
+      <c r="D1116" s="22"/>
     </row>
     <row r="1117">
       <c r="B1117" s="21" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1117" s="22" t="s">
-        <v>777</v>
-      </c>
+      <c r="C1117" s="22"/>
       <c r="D1117" s="22"/>
     </row>
     <row r="1118">
@@ -15218,7 +15214,7 @@
         <v/>
       </c>
       <c r="C1118" s="22" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="D1118" s="22"/>
     </row>
@@ -15227,7 +15223,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1119" s="22"/>
+      <c r="C1119" s="22" t="s">
+        <v>776</v>
+      </c>
       <c r="D1119" s="22"/>
     </row>
     <row r="1120">
@@ -15235,9 +15233,7 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1120" s="22" t="s">
-        <v>755</v>
-      </c>
+      <c r="C1120" s="22"/>
       <c r="D1120" s="22"/>
     </row>
     <row r="1121">
@@ -15246,7 +15242,7 @@
         <v/>
       </c>
       <c r="C1121" s="22" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="D1121" s="22"/>
     </row>
@@ -15264,7 +15260,7 @@
         <v/>
       </c>
       <c r="C1123" s="22" t="s">
-        <v>755</v>
+        <v>777</v>
       </c>
       <c r="D1123" s="22"/>
     </row>
@@ -15282,7 +15278,7 @@
         <v/>
       </c>
       <c r="C1125" s="22" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D1125" s="22"/>
     </row>
@@ -15291,7 +15287,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1126" s="22"/>
+      <c r="C1126" s="22" t="s">
+        <v>779</v>
+      </c>
       <c r="D1126" s="22"/>
     </row>
     <row r="1127">
@@ -15300,17 +15298,17 @@
         <v/>
       </c>
       <c r="C1127" s="22" t="s">
-        <v>781</v>
+        <v>744</v>
       </c>
       <c r="D1127" s="22"/>
     </row>
     <row r="1128">
       <c r="B1128" s="21" t="str">
         <f t="shared" si="17"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1128" s="22" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D1128" s="22"/>
     </row>
@@ -15319,18 +15317,16 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1129" s="22" t="s">
-        <v>747</v>
-      </c>
+      <c r="C1129" s="22"/>
       <c r="D1129" s="22"/>
     </row>
     <row r="1130">
       <c r="B1130" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1130" s="22" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D1130" s="22"/>
     </row>
@@ -15348,7 +15344,7 @@
         <v/>
       </c>
       <c r="C1132" s="22" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="D1132" s="22"/>
     </row>
@@ -15357,7 +15353,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1133" s="22"/>
+      <c r="C1133" s="22" t="s">
+        <v>782</v>
+      </c>
       <c r="D1133" s="22"/>
     </row>
     <row r="1134">
@@ -15365,9 +15363,7 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1134" s="22" t="s">
-        <v>785</v>
-      </c>
+      <c r="C1134" s="22"/>
       <c r="D1134" s="22"/>
     </row>
     <row r="1135">
@@ -15375,7 +15371,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1135" s="22"/>
+      <c r="C1135" s="22" t="s">
+        <v>770</v>
+      </c>
       <c r="D1135" s="22"/>
     </row>
     <row r="1136">
@@ -15383,9 +15381,7 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1136" s="22" t="s">
-        <v>786</v>
-      </c>
+      <c r="C1136" s="22"/>
       <c r="D1136" s="22"/>
     </row>
     <row r="1137">
@@ -15394,18 +15390,16 @@
         <v/>
       </c>
       <c r="C1137" s="22" t="s">
-        <v>747</v>
+        <v>783</v>
       </c>
       <c r="D1137" s="22"/>
     </row>
     <row r="1138">
       <c r="B1138" s="21" t="str">
         <f t="shared" si="17"/>
-        <v>INFO</v>
-      </c>
-      <c r="C1138" s="22" t="s">
-        <v>783</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C1138" s="22"/>
       <c r="D1138" s="22"/>
     </row>
     <row r="1139">
@@ -15413,7 +15407,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1139" s="22"/>
+      <c r="C1139" s="22" t="s">
+        <v>784</v>
+      </c>
       <c r="D1139" s="22"/>
     </row>
     <row r="1140">
@@ -15421,9 +15417,7 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1140" s="22" t="s">
-        <v>787</v>
-      </c>
+      <c r="C1140" s="22"/>
       <c r="D1140" s="22"/>
     </row>
     <row r="1141">
@@ -15431,7 +15425,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1141" s="22"/>
+      <c r="C1141" s="22" t="s">
+        <v>785</v>
+      </c>
       <c r="D1141" s="22"/>
     </row>
     <row r="1142">
@@ -15440,7 +15436,7 @@
         <v/>
       </c>
       <c r="C1142" s="22" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D1142" s="22"/>
     </row>
@@ -15449,9 +15445,7 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1143" s="22" t="s">
-        <v>788</v>
-      </c>
+      <c r="C1143" s="22"/>
       <c r="D1143" s="22"/>
     </row>
     <row r="1144">
@@ -15459,16 +15453,18 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1144" s="22"/>
+      <c r="C1144" s="22" t="s">
+        <v>770</v>
+      </c>
       <c r="D1144" s="22"/>
     </row>
     <row r="1145">
       <c r="B1145" s="21" t="str">
         <f t="shared" si="17"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1145" s="22" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D1145" s="22"/>
     </row>
@@ -15486,7 +15482,7 @@
         <v/>
       </c>
       <c r="C1147" s="22" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D1147" s="22"/>
     </row>
@@ -15504,7 +15500,7 @@
         <v/>
       </c>
       <c r="C1149" s="22" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
       <c r="D1149" s="22"/>
     </row>
@@ -15513,9 +15509,7 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1150" s="22" t="s">
-        <v>791</v>
-      </c>
+      <c r="C1150" s="22"/>
       <c r="D1150" s="22"/>
     </row>
     <row r="1151">
@@ -15523,7 +15517,9 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="C1151" s="22"/>
+      <c r="C1151" s="22" t="s">
+        <v>789</v>
+      </c>
       <c r="D1151" s="22"/>
     </row>
     <row r="1152">
@@ -15532,7 +15528,7 @@
         <v/>
       </c>
       <c r="C1152" s="22" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="D1152" s="22"/>
     </row>
@@ -15550,7 +15546,7 @@
         <v/>
       </c>
       <c r="C1154" s="22" t="s">
-        <v>792</v>
+        <v>770</v>
       </c>
       <c r="D1154" s="22"/>
     </row>
@@ -15560,7 +15556,7 @@
         <v/>
       </c>
       <c r="C1155" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D1155" s="22"/>
     </row>
@@ -15578,7 +15574,7 @@
         <v/>
       </c>
       <c r="C1157" s="22" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="D1157" s="22"/>
     </row>
@@ -15587,9 +15583,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1158" s="22" t="s">
-        <v>794</v>
-      </c>
+      <c r="C1158" s="22"/>
       <c r="D1158" s="22"/>
     </row>
     <row r="1159">
@@ -15597,7 +15591,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1159" s="22"/>
+      <c r="C1159" s="22" t="s">
+        <v>792</v>
+      </c>
       <c r="D1159" s="22"/>
     </row>
     <row r="1160">
@@ -15605,9 +15601,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1160" s="22" t="s">
-        <v>785</v>
-      </c>
+      <c r="C1160" s="22"/>
       <c r="D1160" s="22"/>
     </row>
     <row r="1161">
@@ -15615,16 +15609,18 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1161" s="22"/>
+      <c r="C1161" s="22" t="s">
+        <v>793</v>
+      </c>
       <c r="D1161" s="22"/>
     </row>
     <row r="1162">
       <c r="B1162" s="21" t="str">
         <f t="shared" si="18"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1162" s="22" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D1162" s="22"/>
     </row>
@@ -15642,18 +15638,16 @@
         <v/>
       </c>
       <c r="C1164" s="22" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D1164" s="22"/>
     </row>
     <row r="1165">
       <c r="B1165" s="21" t="str">
         <f t="shared" si="18"/>
-        <v>INFO</v>
-      </c>
-      <c r="C1165" s="22" t="s">
-        <v>797</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C1165" s="22"/>
       <c r="D1165" s="22"/>
     </row>
     <row r="1166">
@@ -15661,7 +15655,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1166" s="22"/>
+      <c r="C1166" s="22" t="s">
+        <v>770</v>
+      </c>
       <c r="D1166" s="22"/>
     </row>
     <row r="1167">
@@ -15670,7 +15666,7 @@
         <v/>
       </c>
       <c r="C1167" s="22" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D1167" s="22"/>
     </row>
@@ -15688,7 +15684,7 @@
         <v/>
       </c>
       <c r="C1169" s="22" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="D1169" s="22"/>
     </row>
@@ -15697,9 +15693,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1170" s="22" t="s">
-        <v>799</v>
-      </c>
+      <c r="C1170" s="22"/>
       <c r="D1170" s="22"/>
     </row>
     <row r="1171">
@@ -15707,7 +15701,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1171" s="22"/>
+      <c r="C1171" s="22" t="s">
+        <v>797</v>
+      </c>
       <c r="D1171" s="22"/>
     </row>
     <row r="1172">
@@ -15715,9 +15711,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1172" s="22" t="s">
-        <v>785</v>
-      </c>
+      <c r="C1172" s="22"/>
       <c r="D1172" s="22"/>
     </row>
     <row r="1173">
@@ -15725,7 +15719,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1173" s="22"/>
+      <c r="C1173" s="22" t="s">
+        <v>758</v>
+      </c>
       <c r="D1173" s="22"/>
     </row>
     <row r="1174">
@@ -15734,7 +15730,7 @@
         <v/>
       </c>
       <c r="C1174" s="22" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D1174" s="22"/>
     </row>
@@ -15743,7 +15739,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1175" s="22"/>
+      <c r="C1175" s="22" t="s">
+        <v>799</v>
+      </c>
       <c r="D1175" s="22"/>
     </row>
     <row r="1176">
@@ -15752,7 +15750,7 @@
         <v/>
       </c>
       <c r="C1176" s="22" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D1176" s="22"/>
     </row>
@@ -15762,7 +15760,7 @@
         <v/>
       </c>
       <c r="C1177" s="22" t="s">
-        <v>801</v>
+        <v>762</v>
       </c>
       <c r="D1177" s="22"/>
     </row>
@@ -15772,7 +15770,7 @@
         <v/>
       </c>
       <c r="C1178" s="22" t="s">
-        <v>802</v>
+        <v>763</v>
       </c>
       <c r="D1178" s="22"/>
     </row>
@@ -15782,7 +15780,7 @@
         <v/>
       </c>
       <c r="C1179" s="22" t="s">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="D1179" s="22"/>
     </row>
@@ -15792,7 +15790,7 @@
         <v/>
       </c>
       <c r="C1180" s="22" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D1180" s="22"/>
     </row>
@@ -15802,7 +15800,7 @@
         <v/>
       </c>
       <c r="C1181" s="22" t="s">
-        <v>765</v>
+        <v>801</v>
       </c>
       <c r="D1181" s="22"/>
     </row>
@@ -15812,7 +15810,7 @@
         <v/>
       </c>
       <c r="C1182" s="22" t="s">
-        <v>803</v>
+        <v>767</v>
       </c>
       <c r="D1182" s="22"/>
     </row>
@@ -15822,7 +15820,7 @@
         <v/>
       </c>
       <c r="C1183" s="22" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D1183" s="22"/>
     </row>
@@ -15831,9 +15829,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1184" s="22" t="s">
-        <v>804</v>
-      </c>
+      <c r="C1184" s="22"/>
       <c r="D1184" s="22"/>
     </row>
     <row r="1185">
@@ -15842,7 +15838,7 @@
         <v/>
       </c>
       <c r="C1185" s="22" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
       <c r="D1185" s="22"/>
     </row>
@@ -15851,9 +15847,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1186" s="22" t="s">
-        <v>770</v>
-      </c>
+      <c r="C1186" s="22"/>
       <c r="D1186" s="22"/>
     </row>
     <row r="1187">
@@ -15861,7 +15855,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1187" s="22"/>
+      <c r="C1187" s="22" t="s">
+        <v>770</v>
+      </c>
       <c r="D1187" s="22"/>
     </row>
     <row r="1188">
@@ -15869,9 +15865,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1188" s="22" t="s">
-        <v>805</v>
-      </c>
+      <c r="C1188" s="22"/>
       <c r="D1188" s="22"/>
     </row>
     <row r="1189">
@@ -15879,7 +15873,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1189" s="22"/>
+      <c r="C1189" s="22" t="s">
+        <v>803</v>
+      </c>
       <c r="D1189" s="22"/>
     </row>
     <row r="1190">
@@ -15887,9 +15883,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1190" s="22" t="s">
-        <v>785</v>
-      </c>
+      <c r="C1190" s="22"/>
       <c r="D1190" s="22"/>
     </row>
     <row r="1191">
@@ -15897,7 +15891,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1191" s="22"/>
+      <c r="C1191" s="22" t="s">
+        <v>804</v>
+      </c>
       <c r="D1191" s="22"/>
     </row>
     <row r="1192">
@@ -15906,7 +15902,7 @@
         <v/>
       </c>
       <c r="C1192" s="22" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D1192" s="22"/>
     </row>
@@ -15924,7 +15920,7 @@
         <v/>
       </c>
       <c r="C1194" s="22" t="s">
-        <v>807</v>
+        <v>770</v>
       </c>
       <c r="D1194" s="22"/>
     </row>
@@ -15933,9 +15929,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1195" s="22" t="s">
-        <v>808</v>
-      </c>
+      <c r="C1195" s="22"/>
       <c r="D1195" s="22"/>
     </row>
     <row r="1196">
@@ -15943,7 +15937,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1196" s="22"/>
+      <c r="C1196" s="22" t="s">
+        <v>806</v>
+      </c>
       <c r="D1196" s="22"/>
     </row>
     <row r="1197">
@@ -15952,7 +15948,7 @@
         <v/>
       </c>
       <c r="C1197" s="22" t="s">
-        <v>785</v>
+        <v>807</v>
       </c>
       <c r="D1197" s="22"/>
     </row>
@@ -15970,7 +15966,7 @@
         <v/>
       </c>
       <c r="C1199" s="22" t="s">
-        <v>809</v>
+        <v>770</v>
       </c>
       <c r="D1199" s="22"/>
     </row>
@@ -15979,9 +15975,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1200" s="22" t="s">
-        <v>810</v>
-      </c>
+      <c r="C1200" s="22"/>
       <c r="D1200" s="22"/>
     </row>
     <row r="1201">
@@ -15989,7 +15983,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1201" s="22"/>
+      <c r="C1201" s="22" t="s">
+        <v>808</v>
+      </c>
       <c r="D1201" s="22"/>
     </row>
     <row r="1202">
@@ -15998,7 +15994,7 @@
         <v/>
       </c>
       <c r="C1202" s="22" t="s">
-        <v>785</v>
+        <v>809</v>
       </c>
       <c r="D1202" s="22"/>
     </row>
@@ -16016,7 +16012,7 @@
         <v/>
       </c>
       <c r="C1204" s="22" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D1204" s="22"/>
     </row>
@@ -16025,9 +16021,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1205" s="22" t="s">
-        <v>812</v>
-      </c>
+      <c r="C1205" s="22"/>
       <c r="D1205" s="22"/>
     </row>
     <row r="1206">
@@ -16035,16 +16029,18 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="C1206" s="22"/>
+      <c r="C1206" s="22" t="s">
+        <v>811</v>
+      </c>
       <c r="D1206" s="22"/>
     </row>
     <row r="1207">
       <c r="B1207" s="21" t="str">
         <f t="shared" si="18"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1207" s="22" t="s">
-        <v>785</v>
+        <v>812</v>
       </c>
       <c r="D1207" s="22"/>
     </row>
@@ -16059,7 +16055,7 @@
     <row r="1209">
       <c r="B1209" s="21" t="str">
         <f t="shared" si="18"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1209" s="22" t="s">
         <v>813</v>
@@ -16069,7 +16065,7 @@
     <row r="1210">
       <c r="B1210" s="21" t="str">
         <f t="shared" si="18"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1210" s="22" t="s">
         <v>814</v>
@@ -16087,7 +16083,7 @@
     <row r="1212">
       <c r="B1212" s="21" t="str">
         <f t="shared" si="18"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1212" s="22" t="s">
         <v>815</v>
@@ -16118,7 +16114,7 @@
         <v/>
       </c>
       <c r="C1215" s="22" t="s">
-        <v>785</v>
+        <v>817</v>
       </c>
       <c r="D1215" s="22"/>
     </row>
@@ -16128,7 +16124,7 @@
         <v/>
       </c>
       <c r="C1216" s="22" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D1216" s="22"/>
     </row>
@@ -16146,17 +16142,17 @@
         <v/>
       </c>
       <c r="C1218" s="22" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D1218" s="22"/>
     </row>
     <row r="1219">
       <c r="B1219" s="21" t="str">
         <f t="shared" ref="B1219:B1282" si="19">IF(LEFT(C1219,1)="#","",IF(ISNUMBER(SEARCH("CRITICAL:",C1219)),"CRITICAL",IF(ISNUMBER(SEARCH("ERROR:",C1219)),"ERROR",IF(ISNUMBER(SEARCH("WARNING:",C1219)),"WARNING",IF(ISNUMBER(SEARCH("INFO:",C1219)),"INFO",IF(ISNUMBER(SEARCH("DEBUG:",C1219)),"DEBUG",""))))))</f>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1219" s="22" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D1219" s="22"/>
     </row>
@@ -16165,7 +16161,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1220" s="22"/>
+      <c r="C1220" s="22" t="s">
+        <v>821</v>
+      </c>
       <c r="D1220" s="22"/>
     </row>
     <row r="1221">
@@ -16173,18 +16171,16 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1221" s="22" t="s">
-        <v>820</v>
-      </c>
+      <c r="C1221" s="22"/>
       <c r="D1221" s="22"/>
     </row>
     <row r="1222">
       <c r="B1222" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1222" s="22" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D1222" s="22"/>
     </row>
@@ -16193,9 +16189,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1223" s="22" t="s">
-        <v>822</v>
-      </c>
+      <c r="C1223" s="22"/>
       <c r="D1223" s="22"/>
     </row>
     <row r="1224">
@@ -16203,16 +16197,18 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1224" s="22"/>
+      <c r="C1224" s="22" t="s">
+        <v>822</v>
+      </c>
       <c r="D1224" s="22"/>
     </row>
     <row r="1225">
       <c r="B1225" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1225" s="22" t="s">
-        <v>820</v>
+        <v>585</v>
       </c>
       <c r="D1225" s="22"/>
     </row>
@@ -16221,7 +16217,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1226" s="22"/>
+      <c r="C1226" s="22" t="s">
+        <v>823</v>
+      </c>
       <c r="D1226" s="22"/>
     </row>
     <row r="1227">
@@ -16230,17 +16228,17 @@
         <v/>
       </c>
       <c r="C1227" s="22" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D1227" s="22"/>
     </row>
     <row r="1228">
       <c r="B1228" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1228" s="22" t="s">
-        <v>588</v>
+        <v>825</v>
       </c>
       <c r="D1228" s="22"/>
     </row>
@@ -16250,7 +16248,7 @@
         <v/>
       </c>
       <c r="C1229" s="22" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D1229" s="22"/>
     </row>
@@ -16260,7 +16258,7 @@
         <v/>
       </c>
       <c r="C1230" s="22" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D1230" s="22"/>
     </row>
@@ -16270,24 +16268,24 @@
         <v/>
       </c>
       <c r="C1231" s="22" t="s">
-        <v>826</v>
+        <v>492</v>
       </c>
       <c r="D1231" s="22"/>
     </row>
     <row r="1232">
       <c r="B1232" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1232" s="22" t="s">
-        <v>827</v>
+        <v>493</v>
       </c>
       <c r="D1232" s="22"/>
     </row>
     <row r="1233">
       <c r="B1233" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1233" s="22" t="s">
         <v>828</v>
@@ -16297,41 +16295,37 @@
     <row r="1234">
       <c r="B1234" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1234" s="22" t="s">
-        <v>492</v>
+        <v>829</v>
       </c>
       <c r="D1234" s="22"/>
     </row>
     <row r="1235">
       <c r="B1235" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
-      </c>
-      <c r="C1235" s="22" t="s">
-        <v>493</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C1235" s="22"/>
       <c r="D1235" s="22"/>
     </row>
     <row r="1236">
       <c r="B1236" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1236" s="22" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D1236" s="22"/>
     </row>
     <row r="1237">
       <c r="B1237" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
-      </c>
-      <c r="C1237" s="22" t="s">
-        <v>830</v>
-      </c>
+        <v/>
+      </c>
+      <c r="C1237" s="22"/>
       <c r="D1237" s="22"/>
     </row>
     <row r="1238">
@@ -16339,34 +16333,38 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1238" s="22"/>
+      <c r="C1238" s="22" t="s">
+        <v>831</v>
+      </c>
       <c r="D1238" s="22"/>
     </row>
     <row r="1239">
       <c r="B1239" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1239" s="22" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D1239" s="22"/>
     </row>
     <row r="1240">
       <c r="B1240" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="C1240" s="22"/>
+        <v>INFO</v>
+      </c>
+      <c r="C1240" s="22" t="s">
+        <v>833</v>
+      </c>
       <c r="D1240" s="22"/>
     </row>
     <row r="1241">
       <c r="B1241" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1241" s="22" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D1241" s="22"/>
     </row>
@@ -16376,99 +16374,98 @@
         <v>INFO</v>
       </c>
       <c r="C1242" s="22" t="s">
-        <v>833</v>
+        <v>585</v>
       </c>
       <c r="D1242" s="22"/>
     </row>
     <row r="1243">
       <c r="B1243" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1243" s="22" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D1243" s="22"/>
     </row>
     <row r="1244">
       <c r="B1244" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1244" s="22" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D1244" s="22"/>
     </row>
     <row r="1245">
       <c r="B1245" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1245" s="22" t="s">
-        <v>588</v>
+        <v>837</v>
       </c>
       <c r="D1245" s="22"/>
     </row>
     <row r="1246">
       <c r="B1246" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1246" s="22" t="s">
-        <v>836</v>
+        <v>482</v>
       </c>
       <c r="D1246" s="22"/>
     </row>
     <row r="1247">
       <c r="B1247" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1247" s="22" t="s">
-        <v>837</v>
+        <v>483</v>
       </c>
       <c r="D1247" s="22"/>
     </row>
     <row r="1248">
       <c r="B1248" s="21" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>WARNING</v>
       </c>
       <c r="C1248" s="22" t="s">
-        <v>838</v>
-      </c>
-      <c r="D1248" s="22"/>
+        <v>484</v>
+      </c>
+      <c r="D1248" s="22" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="1249">
       <c r="B1249" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1249" s="22" t="s">
-        <v>482</v>
+        <v>838</v>
       </c>
       <c r="D1249" s="22"/>
     </row>
     <row r="1250">
       <c r="B1250" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1250" s="22" t="s">
-        <v>483</v>
+        <v>839</v>
       </c>
     </row>
     <row r="1251" ht="30">
       <c r="B1251" s="21" t="str">
         <f t="shared" si="19"/>
-        <v>WARNING</v>
+        <v/>
       </c>
       <c r="C1251" s="22" t="s">
-        <v>484</v>
-      </c>
-      <c r="D1251" s="22" t="s">
-        <v>485</v>
+        <v>840</v>
       </c>
     </row>
     <row r="1252">
@@ -16477,7 +16474,7 @@
         <v/>
       </c>
       <c r="C1252" s="22" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D1252" s="22"/>
     </row>
@@ -16486,9 +16483,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1253" s="22" t="s">
-        <v>840</v>
-      </c>
+      <c r="C1253" s="22"/>
       <c r="D1253" s="22"/>
     </row>
     <row r="1254">
@@ -16507,7 +16502,7 @@
         <v/>
       </c>
       <c r="C1255" s="22" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="D1255" s="22"/>
     </row>
@@ -16516,7 +16511,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1256" s="22"/>
+      <c r="C1256" s="22" t="s">
+        <v>843</v>
+      </c>
       <c r="D1256" s="22"/>
     </row>
     <row r="1257">
@@ -16525,7 +16522,7 @@
         <v/>
       </c>
       <c r="C1257" s="22" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D1257" s="22"/>
     </row>
@@ -16535,7 +16532,7 @@
         <v/>
       </c>
       <c r="C1258" s="22" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D1258" s="22"/>
     </row>
@@ -16545,7 +16542,7 @@
         <v/>
       </c>
       <c r="C1259" s="22" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D1259" s="22"/>
     </row>
@@ -16555,7 +16552,7 @@
         <v/>
       </c>
       <c r="C1260" s="22" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D1260" s="22"/>
     </row>
@@ -16565,7 +16562,7 @@
         <v/>
       </c>
       <c r="C1261" s="22" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D1261" s="22"/>
     </row>
@@ -16575,7 +16572,7 @@
         <v/>
       </c>
       <c r="C1262" s="22" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D1262" s="22"/>
     </row>
@@ -16585,7 +16582,7 @@
         <v/>
       </c>
       <c r="C1263" s="22" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D1263" s="22"/>
     </row>
@@ -16595,7 +16592,7 @@
         <v/>
       </c>
       <c r="C1264" s="22" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D1264" s="22"/>
     </row>
@@ -16604,9 +16601,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1265" s="22" t="s">
-        <v>850</v>
-      </c>
+      <c r="C1265" s="22"/>
       <c r="D1265" s="22"/>
     </row>
     <row r="1266">
@@ -16615,7 +16610,7 @@
         <v/>
       </c>
       <c r="C1266" s="22" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D1266" s="22"/>
     </row>
@@ -16625,7 +16620,7 @@
         <v/>
       </c>
       <c r="C1267" s="22" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D1267" s="22"/>
     </row>
@@ -16634,7 +16629,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1268" s="22"/>
+      <c r="C1268" s="22" t="s">
+        <v>854</v>
+      </c>
       <c r="D1268" s="22"/>
     </row>
     <row r="1269">
@@ -16643,7 +16640,7 @@
         <v/>
       </c>
       <c r="C1269" s="22" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="D1269" s="22"/>
     </row>
@@ -16653,7 +16650,7 @@
         <v/>
       </c>
       <c r="C1270" s="22" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D1270" s="22"/>
     </row>
@@ -16662,9 +16659,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1271" s="22" t="s">
-        <v>855</v>
-      </c>
+      <c r="C1271" s="22"/>
       <c r="D1271" s="22"/>
     </row>
     <row r="1272">
@@ -16672,9 +16667,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1272" s="22" t="s">
-        <v>856</v>
-      </c>
+      <c r="C1272" s="22"/>
       <c r="D1272" s="22"/>
     </row>
     <row r="1273">
@@ -16683,7 +16676,7 @@
         <v/>
       </c>
       <c r="C1273" s="22" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
       <c r="D1273" s="22"/>
     </row>
@@ -16692,7 +16685,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1274" s="22"/>
+      <c r="C1274" s="22" t="s">
+        <v>857</v>
+      </c>
       <c r="D1274" s="22"/>
     </row>
     <row r="1275">
@@ -16700,7 +16695,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1275" s="22"/>
+      <c r="C1275" s="22" t="s">
+        <v>858</v>
+      </c>
       <c r="D1275" s="22"/>
     </row>
     <row r="1276">
@@ -16709,7 +16706,7 @@
         <v/>
       </c>
       <c r="C1276" s="22" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D1276" s="22"/>
     </row>
@@ -16718,9 +16715,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1277" s="22" t="s">
-        <v>858</v>
-      </c>
+      <c r="C1277" s="22"/>
       <c r="D1277" s="22"/>
     </row>
     <row r="1278">
@@ -16738,9 +16733,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1279" s="22" t="s">
-        <v>839</v>
-      </c>
+      <c r="C1279" s="22"/>
       <c r="D1279" s="22"/>
     </row>
     <row r="1280">
@@ -16756,9 +16749,7 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1281" s="22" t="s">
-        <v>860</v>
-      </c>
+      <c r="C1281" s="22"/>
       <c r="D1281" s="22"/>
     </row>
     <row r="1282">
@@ -16766,7 +16757,9 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="C1282" s="22"/>
+      <c r="C1282" s="22" t="s">
+        <v>860</v>
+      </c>
       <c r="D1282" s="22"/>
     </row>
     <row r="1283">
@@ -16782,7 +16775,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1284" s="22"/>
+      <c r="C1284" s="22" t="s">
+        <v>861</v>
+      </c>
       <c r="D1284" s="22"/>
     </row>
     <row r="1285">
@@ -16791,7 +16786,7 @@
         <v/>
       </c>
       <c r="C1285" s="22" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D1285" s="22"/>
     </row>
@@ -16800,7 +16795,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1286" s="22"/>
+      <c r="C1286" s="22" t="s">
+        <v>863</v>
+      </c>
       <c r="D1286" s="22"/>
     </row>
     <row r="1287">
@@ -16809,7 +16806,7 @@
         <v/>
       </c>
       <c r="C1287" s="22" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D1287" s="22"/>
     </row>
@@ -16819,7 +16816,7 @@
         <v/>
       </c>
       <c r="C1288" s="22" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D1288" s="22"/>
     </row>
@@ -16829,7 +16826,7 @@
         <v/>
       </c>
       <c r="C1289" s="22" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D1289" s="22"/>
     </row>
@@ -16839,7 +16836,7 @@
         <v/>
       </c>
       <c r="C1290" s="22" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D1290" s="22"/>
     </row>
@@ -16849,7 +16846,7 @@
         <v/>
       </c>
       <c r="C1291" s="22" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D1291" s="22"/>
     </row>
@@ -16859,7 +16856,7 @@
         <v/>
       </c>
       <c r="C1292" s="22" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D1292" s="22"/>
     </row>
@@ -16869,7 +16866,7 @@
         <v/>
       </c>
       <c r="C1293" s="22" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D1293" s="22"/>
     </row>
@@ -16879,7 +16876,7 @@
         <v/>
       </c>
       <c r="C1294" s="22" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D1294" s="22"/>
     </row>
@@ -16889,7 +16886,7 @@
         <v/>
       </c>
       <c r="C1295" s="22" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D1295" s="22"/>
     </row>
@@ -16899,7 +16896,7 @@
         <v/>
       </c>
       <c r="C1296" s="22" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="D1296" s="22"/>
     </row>
@@ -16909,7 +16906,7 @@
         <v/>
       </c>
       <c r="C1297" s="22" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D1297" s="22"/>
     </row>
@@ -16918,9 +16915,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1298" s="22" t="s">
-        <v>873</v>
-      </c>
+      <c r="C1298" s="22"/>
       <c r="D1298" s="22"/>
     </row>
     <row r="1299">
@@ -16929,7 +16924,7 @@
         <v/>
       </c>
       <c r="C1299" s="22" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="D1299" s="22"/>
     </row>
@@ -16948,7 +16943,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1301" s="22"/>
+      <c r="C1301" s="22" t="s">
+        <v>876</v>
+      </c>
       <c r="D1301" s="22"/>
     </row>
     <row r="1302">
@@ -16956,9 +16953,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1302" s="22" t="s">
-        <v>864</v>
-      </c>
+      <c r="C1302" s="22"/>
       <c r="D1302" s="22"/>
     </row>
     <row r="1303">
@@ -16966,9 +16961,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1303" s="22" t="s">
-        <v>876</v>
-      </c>
+      <c r="C1303" s="22"/>
       <c r="D1303" s="22"/>
     </row>
     <row r="1304">
@@ -16977,7 +16970,7 @@
         <v/>
       </c>
       <c r="C1304" s="22" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="D1304" s="22"/>
     </row>
@@ -16986,7 +16979,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1305" s="22"/>
+      <c r="C1305" s="22" t="s">
+        <v>877</v>
+      </c>
       <c r="D1305" s="22"/>
     </row>
     <row r="1306">
@@ -16994,7 +16989,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1306" s="22"/>
+      <c r="C1306" s="22" t="s">
+        <v>878</v>
+      </c>
       <c r="D1306" s="22"/>
     </row>
     <row r="1307">
@@ -17002,9 +16999,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1307" s="22" t="s">
-        <v>865</v>
-      </c>
+      <c r="C1307" s="22"/>
       <c r="D1307" s="22"/>
     </row>
     <row r="1308">
@@ -17012,9 +17007,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1308" s="22" t="s">
-        <v>878</v>
-      </c>
+      <c r="C1308" s="22"/>
       <c r="D1308" s="22"/>
     </row>
     <row r="1309">
@@ -17023,7 +17016,7 @@
         <v/>
       </c>
       <c r="C1309" s="22" t="s">
-        <v>879</v>
+        <v>865</v>
       </c>
       <c r="D1309" s="22"/>
     </row>
@@ -17032,7 +17025,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1310" s="22"/>
+      <c r="C1310" s="22" t="s">
+        <v>879</v>
+      </c>
       <c r="D1310" s="22"/>
     </row>
     <row r="1311">
@@ -17040,7 +17035,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1311" s="22"/>
+      <c r="C1311" s="22" t="s">
+        <v>880</v>
+      </c>
       <c r="D1311" s="22"/>
     </row>
     <row r="1312">
@@ -17048,9 +17045,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1312" s="22" t="s">
-        <v>866</v>
-      </c>
+      <c r="C1312" s="22"/>
       <c r="D1312" s="22"/>
     </row>
     <row r="1313">
@@ -17058,9 +17053,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1313" s="22" t="s">
-        <v>880</v>
-      </c>
+      <c r="C1313" s="22"/>
       <c r="D1313" s="22"/>
     </row>
     <row r="1314">
@@ -17069,7 +17062,7 @@
         <v/>
       </c>
       <c r="C1314" s="22" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="D1314" s="22"/>
     </row>
@@ -17078,7 +17071,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1315" s="22"/>
+      <c r="C1315" s="22" t="s">
+        <v>881</v>
+      </c>
       <c r="D1315" s="22"/>
     </row>
     <row r="1316">
@@ -17086,7 +17081,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1316" s="22"/>
+      <c r="C1316" s="22" t="s">
+        <v>882</v>
+      </c>
       <c r="D1316" s="22"/>
     </row>
     <row r="1317">
@@ -17094,9 +17091,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1317" s="22" t="s">
-        <v>867</v>
-      </c>
+      <c r="C1317" s="22"/>
       <c r="D1317" s="22"/>
     </row>
     <row r="1318">
@@ -17105,7 +17100,7 @@
         <v/>
       </c>
       <c r="C1318" s="22" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D1318" s="22"/>
     </row>
@@ -17114,9 +17109,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1319" s="22" t="s">
-        <v>883</v>
-      </c>
+      <c r="C1319" s="22"/>
       <c r="D1319" s="22"/>
     </row>
     <row r="1320">
@@ -17133,7 +17126,7 @@
         <v/>
       </c>
       <c r="C1321" s="22" t="s">
-        <v>884</v>
+        <v>867</v>
       </c>
       <c r="D1321" s="22"/>
     </row>
@@ -17142,7 +17135,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1322" s="22"/>
+      <c r="C1322" s="22" t="s">
+        <v>877</v>
+      </c>
       <c r="D1322" s="22"/>
     </row>
     <row r="1323">
@@ -17150,7 +17145,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1323" s="22"/>
+      <c r="C1323" s="22" t="s">
+        <v>884</v>
+      </c>
       <c r="D1323" s="22"/>
     </row>
     <row r="1324">
@@ -17158,9 +17155,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1324" s="22" t="s">
-        <v>868</v>
-      </c>
+      <c r="C1324" s="22"/>
       <c r="D1324" s="22"/>
     </row>
     <row r="1325">
@@ -17169,7 +17164,7 @@
         <v/>
       </c>
       <c r="C1325" s="22" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="D1325" s="22"/>
     </row>
@@ -17178,9 +17173,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1326" s="22" t="s">
-        <v>885</v>
-      </c>
+      <c r="C1326" s="22"/>
       <c r="D1326" s="22"/>
     </row>
     <row r="1327">
@@ -17197,7 +17190,7 @@
         <v/>
       </c>
       <c r="C1328" s="22" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="D1328" s="22"/>
     </row>
@@ -17206,7 +17199,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1329" s="22"/>
+      <c r="C1329" s="22" t="s">
+        <v>886</v>
+      </c>
       <c r="D1329" s="22"/>
     </row>
     <row r="1330">
@@ -17214,7 +17209,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1330" s="22"/>
+      <c r="C1330" s="22" t="s">
+        <v>887</v>
+      </c>
       <c r="D1330" s="22"/>
     </row>
     <row r="1331">
@@ -17222,9 +17219,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1331" s="22" t="s">
-        <v>869</v>
-      </c>
+      <c r="C1331" s="22"/>
       <c r="D1331" s="22"/>
     </row>
     <row r="1332">
@@ -17233,7 +17228,7 @@
         <v/>
       </c>
       <c r="C1332" s="22" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D1332" s="22"/>
     </row>
@@ -17242,9 +17237,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1333" s="22" t="s">
-        <v>888</v>
-      </c>
+      <c r="C1333" s="22"/>
       <c r="D1333" s="22"/>
     </row>
     <row r="1334">
@@ -17252,7 +17245,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1334" s="22"/>
+      <c r="C1334" s="22" t="s">
+        <v>889</v>
+      </c>
       <c r="D1334" s="22"/>
     </row>
     <row r="1335">
@@ -17260,9 +17255,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1335" s="22" t="s">
-        <v>889</v>
-      </c>
+      <c r="C1335" s="22"/>
       <c r="D1335" s="22"/>
     </row>
     <row r="1336">
@@ -17279,7 +17272,7 @@
         <v/>
       </c>
       <c r="C1337" s="22" t="s">
-        <v>890</v>
+        <v>869</v>
       </c>
       <c r="D1337" s="22"/>
     </row>
@@ -17288,7 +17281,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1338" s="22"/>
+      <c r="C1338" s="22" t="s">
+        <v>877</v>
+      </c>
       <c r="D1338" s="22"/>
     </row>
     <row r="1339">
@@ -17296,7 +17291,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1339" s="22"/>
+      <c r="C1339" s="22" t="s">
+        <v>890</v>
+      </c>
       <c r="D1339" s="22"/>
     </row>
     <row r="1340">
@@ -17304,9 +17301,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1340" s="22" t="s">
-        <v>870</v>
-      </c>
+      <c r="C1340" s="22"/>
       <c r="D1340" s="22"/>
     </row>
     <row r="1341">
@@ -17314,9 +17309,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1341" s="22" t="s">
-        <v>878</v>
-      </c>
+      <c r="C1341" s="22"/>
       <c r="D1341" s="22"/>
     </row>
     <row r="1342">
@@ -17325,7 +17318,7 @@
         <v/>
       </c>
       <c r="C1342" s="22" t="s">
-        <v>891</v>
+        <v>870</v>
       </c>
       <c r="D1342" s="22"/>
     </row>
@@ -17334,7 +17327,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1343" s="22"/>
+      <c r="C1343" s="22" t="s">
+        <v>886</v>
+      </c>
       <c r="D1343" s="22"/>
     </row>
     <row r="1344">
@@ -17342,7 +17337,9 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1344" s="22"/>
+      <c r="C1344" s="22" t="s">
+        <v>891</v>
+      </c>
       <c r="D1344" s="22"/>
     </row>
     <row r="1345">
@@ -17350,9 +17347,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1345" s="22" t="s">
-        <v>871</v>
-      </c>
+      <c r="C1345" s="22"/>
       <c r="D1345" s="22"/>
     </row>
     <row r="1346">
@@ -17360,9 +17355,7 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="C1346" s="22" t="s">
-        <v>887</v>
-      </c>
+      <c r="C1346" s="22"/>
       <c r="D1346" s="22"/>
     </row>
     <row r="1347">
@@ -17371,7 +17364,7 @@
         <v/>
       </c>
       <c r="C1347" s="22" t="s">
-        <v>892</v>
+        <v>871</v>
       </c>
       <c r="D1347" s="22"/>
     </row>
@@ -17380,7 +17373,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1348" s="22"/>
+      <c r="C1348" s="22" t="s">
+        <v>892</v>
+      </c>
       <c r="D1348" s="22"/>
     </row>
     <row r="1349">
@@ -17388,7 +17383,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1349" s="22"/>
+      <c r="C1349" s="22" t="s">
+        <v>893</v>
+      </c>
       <c r="D1349" s="22"/>
     </row>
     <row r="1350">
@@ -17396,9 +17393,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1350" s="22" t="s">
-        <v>872</v>
-      </c>
+      <c r="C1350" s="22"/>
       <c r="D1350" s="22"/>
     </row>
     <row r="1351">
@@ -17406,9 +17401,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1351" s="22" t="s">
-        <v>893</v>
-      </c>
+      <c r="C1351" s="22"/>
       <c r="D1351" s="22"/>
     </row>
     <row r="1352">
@@ -17417,7 +17410,7 @@
         <v/>
       </c>
       <c r="C1352" s="22" t="s">
-        <v>894</v>
+        <v>872</v>
       </c>
       <c r="D1352" s="22"/>
     </row>
@@ -17426,7 +17419,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1353" s="22"/>
+      <c r="C1353" s="22" t="s">
+        <v>894</v>
+      </c>
       <c r="D1353" s="22"/>
     </row>
     <row r="1354">
@@ -17434,7 +17429,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1354" s="22"/>
+      <c r="C1354" s="22" t="s">
+        <v>895</v>
+      </c>
       <c r="D1354" s="22"/>
     </row>
     <row r="1355">
@@ -17442,9 +17439,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1355" s="22" t="s">
-        <v>873</v>
-      </c>
+      <c r="C1355" s="22"/>
       <c r="D1355" s="22"/>
     </row>
     <row r="1356">
@@ -17452,9 +17447,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1356" s="22" t="s">
-        <v>895</v>
-      </c>
+      <c r="C1356" s="22"/>
       <c r="D1356" s="22"/>
     </row>
     <row r="1357">
@@ -17463,7 +17456,7 @@
         <v/>
       </c>
       <c r="C1357" s="22" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="D1357" s="22"/>
     </row>
@@ -17472,7 +17465,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1358" s="22"/>
+      <c r="C1358" s="22" t="s">
+        <v>896</v>
+      </c>
       <c r="D1358" s="22"/>
     </row>
     <row r="1359">
@@ -17480,7 +17475,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1359" s="22"/>
+      <c r="C1359" s="22" t="s">
+        <v>897</v>
+      </c>
       <c r="D1359" s="22"/>
     </row>
     <row r="1360">
@@ -17488,9 +17485,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1360" s="22" t="s">
-        <v>874</v>
-      </c>
+      <c r="C1360" s="22"/>
       <c r="D1360" s="22"/>
     </row>
     <row r="1361">
@@ -17498,9 +17493,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1361" s="22" t="s">
-        <v>897</v>
-      </c>
+      <c r="C1361" s="22"/>
       <c r="D1361" s="22"/>
     </row>
     <row r="1362">
@@ -17509,7 +17502,7 @@
         <v/>
       </c>
       <c r="C1362" s="22" t="s">
-        <v>898</v>
+        <v>874</v>
       </c>
       <c r="D1362" s="22"/>
     </row>
@@ -17518,7 +17511,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1363" s="22"/>
+      <c r="C1363" s="22" t="s">
+        <v>898</v>
+      </c>
       <c r="D1363" s="22"/>
     </row>
     <row r="1364">
@@ -17526,7 +17521,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1364" s="22"/>
+      <c r="C1364" s="22" t="s">
+        <v>899</v>
+      </c>
       <c r="D1364" s="22"/>
     </row>
     <row r="1365">
@@ -17534,9 +17531,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1365" s="22" t="s">
-        <v>875</v>
-      </c>
+      <c r="C1365" s="22"/>
       <c r="D1365" s="22"/>
     </row>
     <row r="1366">
@@ -17544,9 +17539,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1366" s="22" t="s">
-        <v>899</v>
-      </c>
+      <c r="C1366" s="22"/>
       <c r="D1366" s="22"/>
     </row>
     <row r="1367">
@@ -17554,9 +17547,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1367" s="22" t="s">
-        <v>900</v>
-      </c>
+      <c r="C1367" s="22"/>
       <c r="D1367" s="22"/>
     </row>
     <row r="1368">
@@ -17564,7 +17555,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1368" s="22"/>
+      <c r="C1368" s="22" t="s">
+        <v>838</v>
+      </c>
       <c r="D1368" s="22"/>
     </row>
     <row r="1369">
@@ -17572,7 +17565,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1369" s="22"/>
+      <c r="C1369" s="22" t="s">
+        <v>900</v>
+      </c>
       <c r="D1369" s="22"/>
     </row>
     <row r="1370">
@@ -17580,7 +17575,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1370" s="22"/>
+      <c r="C1370" s="22" t="s">
+        <v>901</v>
+      </c>
       <c r="D1370" s="22"/>
     </row>
     <row r="1371">
@@ -17589,7 +17586,7 @@
         <v/>
       </c>
       <c r="C1371" s="22" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D1371" s="22"/>
     </row>
@@ -17598,9 +17595,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1372" s="22" t="s">
-        <v>901</v>
-      </c>
+      <c r="C1372" s="22"/>
       <c r="D1372" s="22"/>
     </row>
     <row r="1373">
@@ -17619,7 +17614,7 @@
         <v/>
       </c>
       <c r="C1374" s="22" t="s">
-        <v>839</v>
+        <v>903</v>
       </c>
       <c r="D1374" s="22"/>
     </row>
@@ -17628,7 +17623,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1375" s="22"/>
+      <c r="C1375" s="22" t="s">
+        <v>904</v>
+      </c>
       <c r="D1375" s="22"/>
     </row>
     <row r="1376">
@@ -17636,9 +17633,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1376" s="22" t="s">
-        <v>903</v>
-      </c>
+      <c r="C1376" s="22"/>
       <c r="D1376" s="22"/>
     </row>
     <row r="1377">
@@ -17646,9 +17641,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1377" s="22" t="s">
-        <v>904</v>
-      </c>
+      <c r="C1377" s="22"/>
       <c r="D1377" s="22"/>
     </row>
     <row r="1378">
@@ -17683,7 +17676,7 @@
         <v/>
       </c>
       <c r="C1381" s="22" t="s">
-        <v>906</v>
+        <v>838</v>
       </c>
       <c r="D1381" s="22"/>
     </row>
@@ -17692,7 +17685,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1382" s="22"/>
+      <c r="C1382" s="22" t="s">
+        <v>906</v>
+      </c>
       <c r="D1382" s="22"/>
     </row>
     <row r="1383">
@@ -17700,7 +17695,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1383" s="22"/>
+      <c r="C1383" s="22" t="s">
+        <v>907</v>
+      </c>
       <c r="D1383" s="22"/>
     </row>
     <row r="1384">
@@ -17709,7 +17706,7 @@
         <v/>
       </c>
       <c r="C1384" s="22" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D1384" s="22"/>
     </row>
@@ -17718,9 +17715,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1385" s="22" t="s">
-        <v>907</v>
-      </c>
+      <c r="C1385" s="22"/>
       <c r="D1385" s="22"/>
     </row>
     <row r="1386">
@@ -17739,7 +17734,7 @@
         <v/>
       </c>
       <c r="C1387" s="22" t="s">
-        <v>839</v>
+        <v>909</v>
       </c>
       <c r="D1387" s="22"/>
     </row>
@@ -17748,7 +17743,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1388" s="22"/>
+      <c r="C1388" s="22" t="s">
+        <v>910</v>
+      </c>
       <c r="D1388" s="22"/>
     </row>
     <row r="1389">
@@ -17757,7 +17754,7 @@
         <v/>
       </c>
       <c r="C1389" s="22" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D1389" s="22"/>
     </row>
@@ -17767,7 +17764,7 @@
         <v/>
       </c>
       <c r="C1390" s="22" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D1390" s="22"/>
     </row>
@@ -17777,7 +17774,7 @@
         <v/>
       </c>
       <c r="C1391" s="22" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D1391" s="22"/>
     </row>
@@ -17786,9 +17783,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1392" s="22" t="s">
-        <v>912</v>
-      </c>
+      <c r="C1392" s="22"/>
       <c r="D1392" s="22"/>
     </row>
     <row r="1393">
@@ -17796,9 +17791,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1393" s="22" t="s">
-        <v>913</v>
-      </c>
+      <c r="C1393" s="22"/>
       <c r="D1393" s="22"/>
     </row>
     <row r="1394">
@@ -17807,7 +17800,7 @@
         <v/>
       </c>
       <c r="C1394" s="22" t="s">
-        <v>914</v>
+        <v>838</v>
       </c>
       <c r="D1394" s="22"/>
     </row>
@@ -17816,7 +17809,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1395" s="22"/>
+      <c r="C1395" s="22" t="s">
+        <v>914</v>
+      </c>
       <c r="D1395" s="22"/>
     </row>
     <row r="1396">
@@ -17824,7 +17819,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1396" s="22"/>
+      <c r="C1396" s="22" t="s">
+        <v>915</v>
+      </c>
       <c r="D1396" s="22"/>
     </row>
     <row r="1397">
@@ -17833,7 +17830,7 @@
         <v/>
       </c>
       <c r="C1397" s="22" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D1397" s="22"/>
     </row>
@@ -17842,9 +17839,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1398" s="22" t="s">
-        <v>915</v>
-      </c>
+      <c r="C1398" s="22"/>
       <c r="D1398" s="22"/>
     </row>
     <row r="1399">
@@ -17863,7 +17858,7 @@
         <v/>
       </c>
       <c r="C1400" s="22" t="s">
-        <v>839</v>
+        <v>917</v>
       </c>
       <c r="D1400" s="22"/>
     </row>
@@ -17872,7 +17867,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1401" s="22"/>
+      <c r="C1401" s="22" t="s">
+        <v>918</v>
+      </c>
       <c r="D1401" s="22"/>
     </row>
     <row r="1402">
@@ -17881,7 +17878,7 @@
         <v/>
       </c>
       <c r="C1402" s="22" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D1402" s="22"/>
     </row>
@@ -17891,7 +17888,7 @@
         <v/>
       </c>
       <c r="C1403" s="22" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D1403" s="22"/>
     </row>
@@ -17901,7 +17898,7 @@
         <v/>
       </c>
       <c r="C1404" s="22" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D1404" s="22"/>
     </row>
@@ -17910,9 +17907,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1405" s="22" t="s">
-        <v>920</v>
-      </c>
+      <c r="C1405" s="22"/>
       <c r="D1405" s="22"/>
     </row>
     <row r="1406">
@@ -17920,9 +17915,7 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1406" s="22" t="s">
-        <v>921</v>
-      </c>
+      <c r="C1406" s="22"/>
       <c r="D1406" s="22"/>
     </row>
     <row r="1407">
@@ -17931,7 +17924,7 @@
         <v/>
       </c>
       <c r="C1407" s="22" t="s">
-        <v>922</v>
+        <v>838</v>
       </c>
       <c r="D1407" s="22"/>
     </row>
@@ -17940,7 +17933,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1408" s="22"/>
+      <c r="C1408" s="22" t="s">
+        <v>922</v>
+      </c>
       <c r="D1408" s="22"/>
     </row>
     <row r="1409">
@@ -17948,7 +17943,9 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="C1409" s="22"/>
+      <c r="C1409" s="22" t="s">
+        <v>915</v>
+      </c>
       <c r="D1409" s="22"/>
     </row>
     <row r="1410">
@@ -17957,7 +17954,7 @@
         <v/>
       </c>
       <c r="C1410" s="22" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D1410" s="22"/>
     </row>
@@ -17966,9 +17963,7 @@
         <f t="shared" ref="B1411:B1474" si="22">IF(LEFT(C1411,1)="#","",IF(ISNUMBER(SEARCH("CRITICAL:",C1411)),"CRITICAL",IF(ISNUMBER(SEARCH("ERROR:",C1411)),"ERROR",IF(ISNUMBER(SEARCH("WARNING:",C1411)),"WARNING",IF(ISNUMBER(SEARCH("INFO:",C1411)),"INFO",IF(ISNUMBER(SEARCH("DEBUG:",C1411)),"DEBUG",""))))))</f>
         <v/>
       </c>
-      <c r="C1411" s="22" t="s">
-        <v>923</v>
-      </c>
+      <c r="C1411" s="22"/>
       <c r="D1411" s="22"/>
     </row>
     <row r="1412">
@@ -17977,7 +17972,7 @@
         <v/>
       </c>
       <c r="C1412" s="22" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="D1412" s="22"/>
     </row>
@@ -17987,7 +17982,7 @@
         <v/>
       </c>
       <c r="C1413" s="22" t="s">
-        <v>839</v>
+        <v>924</v>
       </c>
       <c r="D1413" s="22"/>
     </row>
@@ -17996,7 +17991,9 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1414" s="22"/>
+      <c r="C1414" s="22" t="s">
+        <v>925</v>
+      </c>
       <c r="D1414" s="22"/>
     </row>
     <row r="1415">
@@ -18005,7 +18002,7 @@
         <v/>
       </c>
       <c r="C1415" s="22" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D1415" s="22"/>
     </row>
@@ -18015,7 +18012,7 @@
         <v/>
       </c>
       <c r="C1416" s="22" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D1416" s="22"/>
     </row>
@@ -18024,9 +18021,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1417" s="22" t="s">
-        <v>926</v>
-      </c>
+      <c r="C1417" s="22"/>
       <c r="D1417" s="22"/>
     </row>
     <row r="1418">
@@ -18034,9 +18029,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1418" s="22" t="s">
-        <v>927</v>
-      </c>
+      <c r="C1418" s="22"/>
       <c r="D1418" s="22"/>
     </row>
     <row r="1419">
@@ -18045,7 +18038,7 @@
         <v/>
       </c>
       <c r="C1419" s="22" t="s">
-        <v>928</v>
+        <v>838</v>
       </c>
       <c r="D1419" s="22"/>
     </row>
@@ -18054,7 +18047,9 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1420" s="22"/>
+      <c r="C1420" s="22" t="s">
+        <v>928</v>
+      </c>
       <c r="D1420" s="22"/>
     </row>
     <row r="1421">
@@ -18062,7 +18057,9 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1421" s="22"/>
+      <c r="C1421" s="22" t="s">
+        <v>929</v>
+      </c>
       <c r="D1421" s="22"/>
     </row>
     <row r="1422">
@@ -18071,7 +18068,7 @@
         <v/>
       </c>
       <c r="C1422" s="22" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D1422" s="22"/>
     </row>
@@ -18080,9 +18077,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1423" s="22" t="s">
-        <v>929</v>
-      </c>
+      <c r="C1423" s="22"/>
       <c r="D1423" s="22"/>
     </row>
     <row r="1424">
@@ -18101,7 +18096,7 @@
         <v/>
       </c>
       <c r="C1425" s="22" t="s">
-        <v>839</v>
+        <v>931</v>
       </c>
       <c r="D1425" s="22"/>
     </row>
@@ -18110,7 +18105,9 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1426" s="22"/>
+      <c r="C1426" s="22" t="s">
+        <v>932</v>
+      </c>
       <c r="D1426" s="22"/>
     </row>
     <row r="1427">
@@ -18119,7 +18116,7 @@
         <v/>
       </c>
       <c r="C1427" s="22" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="D1427" s="22"/>
     </row>
@@ -18128,9 +18125,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1428" s="22" t="s">
-        <v>932</v>
-      </c>
+      <c r="C1428" s="22"/>
       <c r="D1428" s="22"/>
     </row>
     <row r="1429">
@@ -18138,9 +18133,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1429" s="22" t="s">
-        <v>933</v>
-      </c>
+      <c r="C1429" s="22"/>
       <c r="D1429" s="22"/>
     </row>
     <row r="1430">
@@ -18156,17 +18149,21 @@
     <row r="1431">
       <c r="B1431" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="C1431" s="22"/>
+        <v>INFO</v>
+      </c>
+      <c r="C1431" s="22" t="s">
+        <v>482</v>
+      </c>
       <c r="D1431" s="22"/>
     </row>
     <row r="1432">
       <c r="B1432" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="C1432" s="22"/>
+        <v>INFO</v>
+      </c>
+      <c r="C1432" s="22" t="s">
+        <v>483</v>
+      </c>
       <c r="D1432" s="22"/>
     </row>
     <row r="1433">
@@ -18182,70 +18179,70 @@
     <row r="1434">
       <c r="B1434" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1434" s="22" t="s">
-        <v>482</v>
+        <v>936</v>
       </c>
       <c r="D1434" s="22"/>
     </row>
     <row r="1435">
       <c r="B1435" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1435" s="22" t="s">
-        <v>483</v>
+        <v>937</v>
       </c>
       <c r="D1435" s="22"/>
     </row>
     <row r="1436">
       <c r="B1436" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1436" s="22" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="D1436" s="22"/>
     </row>
     <row r="1437">
       <c r="B1437" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1437" s="22" t="s">
-        <v>937</v>
+        <v>496</v>
       </c>
       <c r="D1437" s="22"/>
     </row>
     <row r="1438">
       <c r="B1438" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1438" s="22" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D1438" s="22"/>
     </row>
     <row r="1439">
       <c r="B1439" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1439" s="22" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D1439" s="22"/>
     </row>
     <row r="1440">
       <c r="B1440" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1440" s="22" t="s">
-        <v>496</v>
+        <v>941</v>
       </c>
       <c r="D1440" s="22"/>
     </row>
@@ -18255,59 +18252,58 @@
         <v>INFO</v>
       </c>
       <c r="C1441" s="22" t="s">
-        <v>940</v>
+        <v>482</v>
       </c>
       <c r="D1441" s="22"/>
     </row>
     <row r="1442">
       <c r="B1442" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1442" s="22" t="s">
-        <v>941</v>
+        <v>483</v>
       </c>
       <c r="D1442" s="22"/>
     </row>
     <row r="1443">
       <c r="B1443" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>WARNING</v>
       </c>
       <c r="C1443" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="D1443" s="22" t="s">
         <v>942</v>
       </c>
-      <c r="D1443" s="22"/>
     </row>
     <row r="1444">
       <c r="B1444" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1444" s="22" t="s">
-        <v>482</v>
+        <v>943</v>
       </c>
       <c r="D1444" s="22"/>
     </row>
     <row r="1445">
       <c r="B1445" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1445" s="22" t="s">
-        <v>483</v>
+        <v>944</v>
       </c>
     </row>
     <row r="1446" ht="30">
       <c r="B1446" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>WARNING</v>
+        <v/>
       </c>
       <c r="C1446" s="22" t="s">
-        <v>484</v>
-      </c>
-      <c r="D1446" s="22" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="1447">
@@ -18315,9 +18311,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1447" s="22" t="s">
-        <v>944</v>
-      </c>
+      <c r="C1447" s="22"/>
       <c r="D1447" s="22"/>
     </row>
     <row r="1448">
@@ -18326,7 +18320,7 @@
         <v/>
       </c>
       <c r="C1448" s="22" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D1448" s="22"/>
     </row>
@@ -18336,7 +18330,7 @@
         <v/>
       </c>
       <c r="C1449" s="22" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D1449" s="22"/>
     </row>
@@ -18345,7 +18339,9 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="C1450" s="22"/>
+      <c r="C1450" s="22" t="s">
+        <v>948</v>
+      </c>
       <c r="D1450" s="22"/>
     </row>
     <row r="1451">
@@ -18354,7 +18350,7 @@
         <v/>
       </c>
       <c r="C1451" s="22" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D1451" s="22"/>
     </row>
@@ -18364,7 +18360,7 @@
         <v/>
       </c>
       <c r="C1452" s="22" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D1452" s="22"/>
     </row>
@@ -18374,17 +18370,17 @@
         <v/>
       </c>
       <c r="C1453" s="22" t="s">
-        <v>949</v>
+        <v>492</v>
       </c>
       <c r="D1453" s="22"/>
     </row>
     <row r="1454">
       <c r="B1454" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1454" s="22" t="s">
-        <v>950</v>
+        <v>493</v>
       </c>
       <c r="D1454" s="22"/>
     </row>
@@ -18401,10 +18397,10 @@
     <row r="1456">
       <c r="B1456" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1456" s="22" t="s">
-        <v>492</v>
+        <v>938</v>
       </c>
       <c r="D1456" s="22"/>
     </row>
@@ -18414,14 +18410,14 @@
         <v>INFO</v>
       </c>
       <c r="C1457" s="22" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D1457" s="22"/>
     </row>
     <row r="1458">
       <c r="B1458" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1458" s="22" t="s">
         <v>952</v>
@@ -18434,17 +18430,17 @@
         <v>INFO</v>
       </c>
       <c r="C1459" s="22" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
       <c r="D1459" s="22"/>
     </row>
     <row r="1460">
       <c r="B1460" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1460" s="22" t="s">
-        <v>496</v>
+        <v>954</v>
       </c>
       <c r="D1460" s="22"/>
     </row>
@@ -18454,17 +18450,17 @@
         <v>INFO</v>
       </c>
       <c r="C1461" s="22" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D1461" s="22"/>
     </row>
     <row r="1462">
       <c r="B1462" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1462" s="22" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D1462" s="22"/>
     </row>
@@ -18474,17 +18470,17 @@
         <v/>
       </c>
       <c r="C1463" s="22" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D1463" s="22"/>
     </row>
     <row r="1464">
       <c r="B1464" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1464" s="22" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="D1464" s="22"/>
     </row>
@@ -18494,7 +18490,7 @@
         <v/>
       </c>
       <c r="C1465" s="22" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D1465" s="22"/>
     </row>
@@ -18504,7 +18500,7 @@
         <v/>
       </c>
       <c r="C1466" s="22" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D1466" s="22"/>
     </row>
@@ -18514,7 +18510,7 @@
         <v/>
       </c>
       <c r="C1467" s="22" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D1467" s="22"/>
     </row>
@@ -18524,27 +18520,27 @@
         <v/>
       </c>
       <c r="C1468" s="22" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D1468" s="22"/>
     </row>
     <row r="1469">
       <c r="B1469" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1469" s="22" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D1469" s="22"/>
     </row>
     <row r="1470">
       <c r="B1470" s="21" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1470" s="22" t="s">
-        <v>962</v>
+        <v>585</v>
       </c>
       <c r="D1470" s="22"/>
     </row>
@@ -18554,27 +18550,27 @@
         <v/>
       </c>
       <c r="C1471" s="22" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D1471" s="22"/>
     </row>
     <row r="1472">
       <c r="B1472" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1472" s="22" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D1472" s="22"/>
     </row>
     <row r="1473">
       <c r="B1473" s="21" t="str">
         <f t="shared" si="22"/>
-        <v>INFO</v>
+        <v/>
       </c>
       <c r="C1473" s="22" t="s">
-        <v>588</v>
+        <v>966</v>
       </c>
       <c r="D1473" s="22"/>
     </row>
@@ -18584,7 +18580,7 @@
         <v/>
       </c>
       <c r="C1474" s="22" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D1474" s="22"/>
     </row>
@@ -18594,7 +18590,7 @@
         <v/>
       </c>
       <c r="C1475" s="22" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D1475" s="22"/>
     </row>
@@ -18604,7 +18600,7 @@
         <v/>
       </c>
       <c r="C1476" s="22" t="s">
-        <v>967</v>
+        <v>66</v>
       </c>
       <c r="D1476" s="22"/>
     </row>
@@ -18614,7 +18610,7 @@
         <v/>
       </c>
       <c r="C1477" s="22" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D1477" s="22"/>
     </row>
@@ -18624,17 +18620,17 @@
         <v/>
       </c>
       <c r="C1478" s="22" t="s">
-        <v>969</v>
+        <v>68</v>
       </c>
       <c r="D1478" s="22"/>
     </row>
     <row r="1479">
       <c r="B1479" s="21" t="str">
         <f t="shared" si="23"/>
-        <v/>
+        <v>INFO</v>
       </c>
       <c r="C1479" s="22" t="s">
-        <v>66</v>
+        <v>970</v>
       </c>
       <c r="D1479" s="22"/>
     </row>
@@ -18644,7 +18640,7 @@
         <v/>
       </c>
       <c r="C1480" s="22" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="D1480" s="22"/>
     </row>
